--- a/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
+++ b/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\fic\chatgpt\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A08597-AE60-446E-9F30-7A2A41978973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E1F070-5BDB-4168-A517-F191CCFCEF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Técnicos</t>
-  </si>
-  <si>
-    <t>4. Demonstrar autonomia</t>
   </si>
   <si>
     <t>TABELA DE NÍVEIS DE DESEMPENHO</t>
@@ -126,12 +123,6 @@
     <t>Assinatura e Carimbo</t>
   </si>
   <si>
-    <t>Socio Emocionais</t>
-  </si>
-  <si>
-    <t>Contextualização:</t>
-  </si>
-  <si>
     <t>Desafios:</t>
   </si>
   <si>
@@ -159,45 +150,6 @@
     <t>Carga Horária Não-Presencial: 0</t>
   </si>
   <si>
-    <t>1. Preparar dados de acordo com fontes de dados variadas.</t>
-  </si>
-  <si>
-    <t>2. Criar modelo de dados por meio da extração, transformação e limpeza de dados.</t>
-  </si>
-  <si>
-    <t>3. Fornecer representações visu-ais dos dados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Implantar ativos </t>
-  </si>
-  <si>
-    <t>Preparou os dados utilizando variados tipos de fontes de informação.</t>
-  </si>
-  <si>
-    <t>Utilizou a ferramenta Power Query para a tratativa das co-lunas e linhas visando corrigir informações inconsistentes.</t>
-  </si>
-  <si>
-    <t>Utilizou a criação de relacio-namento entre tabelas para manipular dados em tabelas distintas.</t>
-  </si>
-  <si>
-    <t>Forneceu representações visu-ais utilizando relatórios com formatação condicional, per-sonalização de temas, indica-dores para praticidade e seg-mentação de dados</t>
-  </si>
-  <si>
-    <t>Implementou o gerenciamento de workspaces e configurou funções visando Modo de distribuição, Rótulos de confi-dencialidade, Alertas de da-dos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Demonstrar autogestão </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Demonstrar pensamento analí-tico </t>
-  </si>
-  <si>
-    <t>3. Demonstrar inteligência emocional</t>
-  </si>
-  <si>
-    <t>Demonstrou autonomia ao conseguir realizar as tarefas praticas relacionadas a tratati-va de dados e manipulação de dados.</t>
-  </si>
-  <si>
     <t>Acertou todos os critérios críticos e pelo menos 1 dos 4 desejáveis</t>
   </si>
   <si>
@@ -205,40 +157,6 @@
   </si>
   <si>
     <t>Avaliação Formativa - Situação Problema</t>
-  </si>
-  <si>
-    <t>Criou modelos de dados utili-zando propriedades de tabelas, cálculo de modelo (DAX), agregação única, manipulação de filtros, inteligência de da-dos temporais.</t>
-  </si>
-  <si>
-    <t>[Capacidade: 1. Demonstrar autogestão]
-[Capacidade: 2. Demonstrar pensamento analí-tico]
-Apresente ao seu instrutor uma visualização semelhante a da imagem acima, contendo:
-- Visual / gráfico de barras comparando as somas das quantidades por nome do produto
-- Visual de carrocel de imagens com as fotos dos produtos
-- Um gráfico de indicador com as médias dos pedidos comparada com o menor e maior pedidos.
-- Gráfico de colunas que compare as somas das quantidades de produtos
-- Gáfico de colunas com a contagem de pedidos por dia
-- Cartões com as somas dos subtotais e a média de valor unitário dos produtos
-[Capacidade: 3. Demonstrar inteligência emocional]
-[Capacidade: 4. Demonstrar autonomia]</t>
-  </si>
-  <si>
-    <t>Resolveu os problemas críti-cos propostos individualmente</t>
-  </si>
-  <si>
-    <t>Resolveu os proble-mas complexos de dados e funções DAX.</t>
-  </si>
-  <si>
-    <t>Demonstrou autogestão ao se propor e realizar as tarefas praticas</t>
-  </si>
-  <si>
-    <t>Demonstrou pensamento analí-tico relacionando as ferramentas do Power BI aos problemas apresentados</t>
-  </si>
-  <si>
-    <t>Demonstrou inteligência emo-cional ao realizar tarefas com-plexas de dados</t>
-  </si>
-  <si>
-    <t>Demonstrou inteligência ao aplicar lógica para resolução de problemas</t>
   </si>
   <si>
     <t>O Curso de Aperfeiçoamento Profissional de Inteligências artificiais generativas aplicada a programação – ChatGPT tem por objetivo a implementação de soluções de desenvolvimento por meio de inteligência artificial generativa, identificando e corrigindo erros comuns em scripts, reescrevendo códigos com intuito de melhorar a compreensão de sua escrita e desempenho geral de aplicação, aprimorando o aprendizado de novas tecnologias, como linguagens de programação, bibliotecas, frameworks e documentações no geral. Além disso, o profissional pode aplicar o treinamento personalizado do ChatGPT por meio da API da OpenAI com intuito de criar e disponibilizar um chatbot de prompt de texto para diversas necessidades de mercado.</t>
@@ -355,6 +273,108 @@
   <si>
     <t>Aula expositiva, demonstração e atividade prática, projeto e portfolio</t>
   </si>
+  <si>
+    <t>Contextualização: Chatbot com Gemini</t>
+  </si>
+  <si>
+    <t>Nossas interações por smartphones, redes sociais via internet estão em constante mudanças que quase não percebemos se estamos interagindo com outras pessoas ou IA, muitos cargos e funções como telefonista, acessorista e outros se tornaram obsoletos, mas a tecnologia de IA tem se tornado cada vez mais presente em nossas vidas, e é importante que os profissionais estejam preparados para lidar com essas tecnologias e utilizá-las de forma eficiente. O ChatGPT é uma ferramenta poderosa que pode ser utilizada para melhorar a produtividade e eficiência em diversas áreas, como desenvolvimento de software, atendimento ao cliente, entre outras. Por isso, é fundamental que os profissionais estejam capacitados para utilizar o ChatGPT e outras ferramentas de IA de forma eficaz, para aproveitar ao máximo seus benefícios e se destacar no mercado de trabalho.</t>
+  </si>
+  <si>
+    <t>Criar um chatbot utilizando o Gemini, que seja capaz de responder a perguntas e realizar tarefas específicas, como agendamento de compromissos, fornecimento de informações sobre produtos ou serviços, entre outras funcionalidades. O chatbot deve ser treinado para entender e responder a diferentes tipos de perguntas e solicitações, utilizando técnicas de processamento de linguagem natural (NLP) para garantir uma comunicação eficaz com os usuários. Além disso, o chatbot deve ser implementado em uma plataforma acessível, um site implantado no GitHub Pages, para que os usuários possam interagir com ele facilmente.
+- Utilizaremos o Gemini e o GitHub Pages por serem gratuitos, acessíveis e fáceis de usar, permitindo que os alunos possam criar e implantar seus chatbots sem a necessidade de conhecimentos avançados em programação ou infraestrutura. O Gemini é uma plataforma de chatbot baseada em IA que oferece recursos avançados de NLP, enquanto o GitHub Pages é um serviço de hospedagem gratuito que permite aos usuários criar e publicar sites estáticos diretamente a partir de seus repositórios do GitHub. Juntos, essas ferramentas proporcionam uma solução prática e eficiente para o desenvolvimento e implantação de chatbots personalizados.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Capacidades técnicas:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+[1 Identificar inteligências artificiais generativas, suas arquiteturas e funcionamento.]
+[2 Treinar IA , utilizando os fundamentos do aprendizado de máquina]
+[3 Criar um chatbot personalizado utilizando o processamento de linguagem natural (NLP)]
+[4 Estruturar e codificar solução utilizando inteligências artificiais]
+[5 Corrigir erros em scripts, builds e deploys com ChatGPT.]
+[6 Refatorar códigos com ChatGPT.]
+[7 Aplicar o processo de treinamento personalizado do ChatGPT através de API, incluindo a coleta e pré-processamento de dados, ajuste de parâmetros, e avaliação do modelo e redes neurais.]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Entrega: 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Chatbot funcional utilizando o Gemini, capaz de responder a perguntas e realizar tarefas específicas.
+Capacidades técnicas:
+[8 Implementar o ChatGPT em aplicações de chatbot usando suas bibliotecas e APIs.]
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Entrega: 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Site implantado no GitHub Pages, onde o chatbot estará disponível para interação com os usuários.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Capacidade sociais, organizativas e metodológicas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+[1 Demonstração raciocínio lógico.]
+[2 Demonstrar atenção aos detalhes.]</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -364,7 +384,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,12 +547,6 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -751,15 +765,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -984,19 +989,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1086,12 +1078,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1119,193 +1133,170 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1321,196 +1312,168 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1775,7 +1738,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AA955"/>
+  <dimension ref="A2:AA960"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.09765625" customWidth="1"/>
@@ -1792,134 +1755,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="135" t="s">
+      <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="132" t="s">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="133"/>
-      <c r="C3" s="140" t="s">
-        <v>70</v>
+      <c r="B3" s="50"/>
+      <c r="C3" s="38" t="s">
+        <v>46</v>
       </c>
-      <c r="D3" s="136"/>
-      <c r="E3" s="126" t="s">
-        <v>68</v>
+      <c r="D3" s="39"/>
+      <c r="E3" s="43" t="s">
+        <v>44</v>
       </c>
-      <c r="F3" s="127"/>
-      <c r="G3" s="134" t="s">
+      <c r="F3" s="44"/>
+      <c r="G3" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134" t="s">
+      <c r="J3" s="36"/>
+    </row>
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="48"/>
+      <c r="G4" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="51"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="42"/>
+      <c r="E5" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="67"/>
+      <c r="G5" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="134"/>
-    </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="132"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="130" t="s">
-        <v>69</v>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+    </row>
+    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="55"/>
+      <c r="B6" s="56"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="68" t="s">
+        <v>37</v>
       </c>
-      <c r="F4" s="131"/>
-      <c r="G4" s="115" t="s">
-        <v>67</v>
+      <c r="F6" s="69"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="54" t="s">
+        <v>25</v>
       </c>
-      <c r="H4" s="115"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-    </row>
-    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="119" t="s">
-        <v>3</v>
+      <c r="B7" s="55"/>
+      <c r="C7" s="58" t="s">
+        <v>41</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="141" t="s">
-        <v>70</v>
+      <c r="D7" s="58"/>
+      <c r="E7" s="45" t="s">
+        <v>47</v>
       </c>
-      <c r="D5" s="116"/>
-      <c r="E5" s="139" t="s">
-        <v>66</v>
+      <c r="F7" s="46"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+    </row>
+    <row r="8" spans="1:27" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+    </row>
+    <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="59" t="s">
+        <v>32</v>
       </c>
-      <c r="F5" s="123"/>
-      <c r="G5" s="115" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-    </row>
-    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="124" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="125"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-    </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="119" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="120" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="120"/>
-      <c r="E7" s="128" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" s="129"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="116"/>
-    </row>
-    <row r="8" spans="1:27" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="129"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="116"/>
-    </row>
-    <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
@@ -1929,7 +1892,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>4</v>
@@ -1940,14 +1903,14 @@
       <c r="F10" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="122" t="s">
+      <c r="G10" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="122"/>
-      <c r="I10" s="122" t="s">
+      <c r="H10" s="60"/>
+      <c r="I10" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="122"/>
+      <c r="J10" s="60"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1967,32 +1930,32 @@
       <c r="AA10" s="1"/>
     </row>
     <row r="11" spans="1:27" ht="255" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="145" t="s">
-        <v>78</v>
+      <c r="A11" s="31" t="s">
+        <v>54</v>
       </c>
       <c r="B11" s="24">
         <v>8</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
-      <c r="E11" s="142" t="s">
-        <v>73</v>
+      <c r="E11" s="30" t="s">
+        <v>49</v>
       </c>
-      <c r="F11" s="150" t="s">
-        <v>74</v>
+      <c r="F11" s="107" t="s">
+        <v>50</v>
       </c>
-      <c r="G11" s="51" t="s">
-        <v>77</v>
+      <c r="G11" s="63" t="s">
+        <v>53</v>
       </c>
-      <c r="H11" s="50"/>
-      <c r="I11" s="143" t="s">
-        <v>76</v>
+      <c r="H11" s="64"/>
+      <c r="I11" s="61" t="s">
+        <v>52</v>
       </c>
-      <c r="J11" s="144"/>
+      <c r="J11" s="62"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2012,26 +1975,26 @@
       <c r="AA11" s="1"/>
     </row>
     <row r="12" spans="1:27" ht="132" x14ac:dyDescent="0.25">
-      <c r="A12" s="146" t="s">
-        <v>81</v>
+      <c r="A12" s="32" t="s">
+        <v>57</v>
       </c>
       <c r="B12" s="2">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
-      <c r="D12" s="147" t="s">
-        <v>85</v>
+      <c r="D12" s="33" t="s">
+        <v>61</v>
       </c>
-      <c r="E12" s="153" t="s">
-        <v>88</v>
+      <c r="E12" s="110" t="s">
+        <v>64</v>
       </c>
-      <c r="F12" s="151"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="118"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="53"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2051,24 +2014,24 @@
       <c r="AA12" s="3"/>
     </row>
     <row r="13" spans="1:27" ht="267.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="146" t="s">
-        <v>83</v>
+      <c r="A13" s="32" t="s">
+        <v>59</v>
       </c>
       <c r="B13" s="14">
         <v>16</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
-      <c r="D13" s="147" t="s">
-        <v>86</v>
+      <c r="D13" s="33" t="s">
+        <v>62</v>
       </c>
-      <c r="E13" s="149"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="33"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="103"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2088,26 +2051,26 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="146" t="s">
-        <v>84</v>
+      <c r="A14" s="32" t="s">
+        <v>60</v>
       </c>
       <c r="B14" s="14">
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
-      <c r="D14" s="148" t="s">
-        <v>87</v>
+      <c r="D14" s="34" t="s">
+        <v>63</v>
       </c>
-      <c r="E14" s="154" t="s">
-        <v>89</v>
+      <c r="E14" s="35" t="s">
+        <v>65</v>
       </c>
-      <c r="F14" s="152"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="33"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="103"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2128,7 +2091,7 @@
     </row>
     <row r="15" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" s="29">
         <f>SUM(B8:B14)</f>
@@ -2138,10 +2101,10 @@
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="16"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2161,18 +2124,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
-        <v>56</v>
+      <c r="A16" s="104" t="s">
+        <v>40</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="67"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="106"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2192,18 +2155,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="68" t="s">
-        <v>31</v>
+      <c r="A17" s="94" t="s">
+        <v>66</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="95"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2222,17 +2185,19 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="60"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
+    <row r="18" spans="1:27" ht="76.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="86" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2252,18 +2217,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="68" t="s">
-        <v>32</v>
+      <c r="A19" s="95" t="s">
+        <v>29</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="95"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2282,17 +2247,19 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="1:27" ht="239.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="60"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
+    <row r="20" spans="1:27" ht="116.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="87"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" s="87"/>
+      <c r="J20" s="87"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2312,18 +2279,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
-        <v>33</v>
+      <c r="A21" s="95" t="s">
+        <v>30</v>
       </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="95"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="95"/>
+      <c r="J21" s="95"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2342,17 +2309,19 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="1:27" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="107"/>
-      <c r="B22" s="107"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
+    <row r="22" spans="1:27" ht="228.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="86"/>
+      <c r="F22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="86"/>
+      <c r="I22" s="86"/>
+      <c r="J22" s="86"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2371,19 +2340,17 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="1:27" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A23" s="107" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
+    <row r="23" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="91"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="93"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2402,19 +2369,19 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="1:27" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
-        <v>58</v>
+    <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="99" t="s">
+        <v>31</v>
       </c>
-      <c r="B24" s="75"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="76"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2433,17 +2400,23 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="104"/>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="106"/>
+    <row r="25" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
+      <c r="D25" s="90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="100" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="101"/>
+      <c r="I25" s="101"/>
+      <c r="J25" s="101"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2462,20 +2435,26 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="113" t="s">
-        <v>34</v>
+    <row r="26" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A26" s="89"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="22">
+        <v>1</v>
       </c>
-      <c r="B26" s="113"/>
-      <c r="C26" s="113"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="113"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="1"/>
+      <c r="H26" s="22">
+        <v>2</v>
+      </c>
+      <c r="I26" s="23">
+        <v>3</v>
+      </c>
+      <c r="J26" s="23">
+        <v>4</v>
+      </c>
+      <c r="K26" s="5"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2493,23 +2472,19 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="71" t="s">
-        <v>36</v>
+    <row r="27" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="77" t="s">
+        <v>11</v>
       </c>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="73" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="114" t="s">
-        <v>37</v>
-      </c>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="133"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -2528,26 +2503,18 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A28" s="72"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="22">
-        <v>1</v>
-      </c>
-      <c r="H28" s="22">
-        <v>2</v>
-      </c>
-      <c r="I28" s="23">
-        <v>3</v>
-      </c>
-      <c r="J28" s="23">
-        <v>4</v>
-      </c>
-      <c r="K28" s="5"/>
+    <row r="28" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="78"/>
+      <c r="B28" s="124"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -2565,21 +2532,17 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="97" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="100"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="102" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="103"/>
-      <c r="F29" s="46"/>
+    <row r="29" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="78"/>
+      <c r="B29" s="125"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="98"/>
       <c r="G29" s="7"/>
       <c r="H29" s="19"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2598,17 +2561,13 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="98"/>
-      <c r="B30" s="108" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="101"/>
-      <c r="D30" s="102" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="103"/>
-      <c r="F30" s="46"/>
+    <row r="30" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="78"/>
+      <c r="B30" s="124"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="97"/>
+      <c r="F30" s="98"/>
       <c r="G30" s="7"/>
       <c r="H30" s="19"/>
       <c r="I30" s="15"/>
@@ -2631,15 +2590,13 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="98"/>
-      <c r="B31" s="100"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="103"/>
-      <c r="F31" s="46"/>
+    <row r="31" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="78"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="98"/>
       <c r="G31" s="7"/>
       <c r="H31" s="19"/>
       <c r="I31" s="15"/>
@@ -2662,17 +2619,13 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="98"/>
-      <c r="B32" s="69" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="70"/>
-      <c r="D32" s="110" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" s="111"/>
-      <c r="F32" s="112"/>
+    <row r="32" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="78"/>
+      <c r="B32" s="124"/>
+      <c r="C32" s="132"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="98"/>
       <c r="G32" s="7"/>
       <c r="H32" s="19"/>
       <c r="I32" s="15"/>
@@ -2695,17 +2648,13 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="98"/>
-      <c r="B33" s="69" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="85" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="86"/>
-      <c r="F33" s="87"/>
+    <row r="33" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="78"/>
+      <c r="B33" s="125"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="98"/>
       <c r="G33" s="7"/>
       <c r="H33" s="19"/>
       <c r="I33" s="15"/>
@@ -2728,17 +2677,13 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="99"/>
-      <c r="B34" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="89"/>
-      <c r="D34" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="91"/>
-      <c r="F34" s="92"/>
+    <row r="34" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="78"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="132"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="98"/>
       <c r="G34" s="7"/>
       <c r="H34" s="19"/>
       <c r="I34" s="15"/>
@@ -2761,19 +2706,13 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="40"/>
+    <row r="35" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="78"/>
+      <c r="B35" s="125"/>
+      <c r="C35" s="131"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="98"/>
       <c r="G35" s="7"/>
       <c r="H35" s="19"/>
       <c r="I35" s="15"/>
@@ -2796,15 +2735,13 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="93" t="s">
-        <v>59</v>
-      </c>
-      <c r="E36" s="94"/>
-      <c r="F36" s="95"/>
+    <row r="36" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="78"/>
+      <c r="B36" s="124"/>
+      <c r="C36" s="132"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="97"/>
+      <c r="F36" s="98"/>
       <c r="G36" s="7"/>
       <c r="H36" s="19"/>
       <c r="I36" s="15"/>
@@ -2827,17 +2764,13 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
-      <c r="B37" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="E37" s="46"/>
-      <c r="F37" s="46"/>
+    <row r="37" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="78"/>
+      <c r="B37" s="125"/>
+      <c r="C37" s="131"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="98"/>
       <c r="G37" s="7"/>
       <c r="H37" s="19"/>
       <c r="I37" s="15"/>
@@ -2860,15 +2793,13 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="96" t="s">
-        <v>60</v>
-      </c>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
+    <row r="38" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="78"/>
+      <c r="B38" s="124"/>
+      <c r="C38" s="132"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="97"/>
+      <c r="F38" s="98"/>
       <c r="G38" s="7"/>
       <c r="H38" s="19"/>
       <c r="I38" s="15"/>
@@ -2891,17 +2822,13 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
-      <c r="B39" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="48"/>
-      <c r="D39" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
+    <row r="39" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="78"/>
+      <c r="B39" s="125"/>
+      <c r="C39" s="131"/>
+      <c r="D39" s="96"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="98"/>
       <c r="G39" s="7"/>
       <c r="H39" s="19"/>
       <c r="I39" s="15"/>
@@ -2924,15 +2851,13 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="96" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
+    <row r="40" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="78"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="132"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="98"/>
       <c r="G40" s="7"/>
       <c r="H40" s="19"/>
       <c r="I40" s="15"/>
@@ -2955,17 +2880,13 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="39"/>
-      <c r="F41" s="40"/>
+    <row r="41" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="78"/>
+      <c r="B41" s="125"/>
+      <c r="C41" s="131"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="97"/>
+      <c r="F41" s="98"/>
       <c r="G41" s="7"/>
       <c r="H41" s="19"/>
       <c r="I41" s="15"/>
@@ -2988,17 +2909,17 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="83"/>
-      <c r="B42" s="84"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+    <row r="42" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="78"/>
+      <c r="B42" s="124"/>
+      <c r="C42" s="132"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="97"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -3017,21 +2938,17 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="79" t="s">
-        <v>13</v>
-      </c>
-      <c r="B43" s="80"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="80"/>
-      <c r="H43" s="81"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+    <row r="43" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="122"/>
+      <c r="B43" s="123"/>
+      <c r="C43" s="133"/>
+      <c r="D43" s="129"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="130"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -3050,23 +2967,17 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>5</v>
-      </c>
-      <c r="B44" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="54">
-        <v>100</v>
-      </c>
-      <c r="G44" s="39"/>
-      <c r="H44" s="40"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
+    <row r="44" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="122"/>
+      <c r="B44" s="124"/>
+      <c r="C44" s="132"/>
+      <c r="D44" s="126"/>
+      <c r="E44" s="127"/>
+      <c r="F44" s="128"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -3085,23 +2996,17 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
-        <v>4</v>
-      </c>
-      <c r="B45" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="40"/>
-      <c r="F45" s="54">
-        <v>80</v>
-      </c>
-      <c r="G45" s="39"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
+    <row r="45" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="122"/>
+      <c r="B45" s="125"/>
+      <c r="C45" s="131"/>
+      <c r="D45" s="129"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="130"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -3120,23 +3025,17 @@
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
     </row>
-    <row r="46" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8">
-        <v>3</v>
-      </c>
-      <c r="B46" s="78" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="54">
-        <v>65</v>
-      </c>
-      <c r="G46" s="39"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+    <row r="46" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="122"/>
+      <c r="B46" s="124"/>
+      <c r="C46" s="132"/>
+      <c r="D46" s="126"/>
+      <c r="E46" s="127"/>
+      <c r="F46" s="128"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -3156,20 +3055,14 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8">
-        <v>2</v>
-      </c>
-      <c r="B47" s="77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="40"/>
-      <c r="F47" s="54">
-        <v>50</v>
-      </c>
-      <c r="G47" s="39"/>
-      <c r="H47" s="40"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
+      <c r="D47" s="75"/>
+      <c r="E47" s="75"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="75"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3191,20 +3084,18 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="8">
-        <v>1</v>
+      <c r="A48" s="70" t="s">
+        <v>12</v>
       </c>
-      <c r="B48" s="53" t="s">
-        <v>17</v>
+      <c r="B48" s="71"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="73" t="s">
+        <v>13</v>
       </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="40"/>
-      <c r="F48" s="54">
-        <v>30</v>
-      </c>
-      <c r="G48" s="39"/>
-      <c r="H48" s="40"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="72"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3225,15 +3116,21 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
     </row>
-    <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
+    <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>5</v>
+      </c>
+      <c r="B49" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="83">
+        <v>100</v>
+      </c>
+      <c r="G49" s="81"/>
+      <c r="H49" s="82"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -3255,20 +3152,20 @@
       <c r="AA49" s="1"/>
     </row>
     <row r="50" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="17" t="s">
-        <v>18</v>
+      <c r="A50" s="8">
+        <v>4</v>
       </c>
-      <c r="E50" s="17" t="s">
-        <v>19</v>
+      <c r="B50" s="85" t="s">
+        <v>39</v>
       </c>
-      <c r="F50" s="17" t="s">
-        <v>20</v>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="82"/>
+      <c r="F50" s="83">
+        <v>80</v>
       </c>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="82"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3290,24 +3187,20 @@
       <c r="AA50" s="1"/>
     </row>
     <row r="51" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="18" t="s">
-        <v>21</v>
+      <c r="A51" s="8">
+        <v>3</v>
       </c>
-      <c r="E51" s="55">
-        <v>1</v>
+      <c r="B51" s="85" t="s">
+        <v>38</v>
       </c>
-      <c r="F51" s="55">
-        <v>0</v>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="82"/>
+      <c r="F51" s="83">
+        <v>65</v>
       </c>
-      <c r="G51" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="36" t="s">
-        <v>23</v>
-      </c>
+      <c r="G51" s="81"/>
+      <c r="H51" s="82"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3329,16 +3222,20 @@
       <c r="AA51" s="1"/>
     </row>
     <row r="52" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="27" t="s">
-        <v>24</v>
+      <c r="A52" s="8">
+        <v>2</v>
       </c>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="59"/>
+      <c r="B52" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="82"/>
+      <c r="F52" s="83">
+        <v>50</v>
+      </c>
+      <c r="G52" s="81"/>
+      <c r="H52" s="82"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3359,19 +3256,23 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
     </row>
-    <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="52" t="s">
-        <v>39</v>
+    <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>1</v>
       </c>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
-      <c r="I53" s="52"/>
-      <c r="J53" s="52"/>
+      <c r="B53" s="84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="82"/>
+      <c r="F53" s="83">
+        <v>30</v>
+      </c>
+      <c r="G53" s="81"/>
+      <c r="H53" s="82"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -3391,16 +3292,16 @@
       <c r="AA53" s="1"/>
     </row>
     <row r="54" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="52"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="52"/>
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -3419,15 +3320,21 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
     </row>
-    <row r="55" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="4"/>
+    <row r="55" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3448,15 +3355,25 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="4"/>
+    <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="113">
+        <v>1</v>
+      </c>
+      <c r="F56" s="113">
+        <v>0</v>
+      </c>
+      <c r="G56" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="116" t="s">
+        <v>22</v>
+      </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -3477,15 +3394,17 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
     </row>
-    <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="4"/>
+    <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="115"/>
+      <c r="H57" s="117"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -3507,16 +3426,18 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
+      <c r="A58" s="112" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="112"/>
+      <c r="C58" s="112"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="112"/>
+      <c r="H58" s="112"/>
+      <c r="I58" s="112"/>
+      <c r="J58" s="112"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3536,16 +3457,16 @@
       <c r="AA58" s="1"/>
     </row>
     <row r="59" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
+      <c r="H59" s="112"/>
+      <c r="I59" s="112"/>
+      <c r="J59" s="112"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -7102,150 +7023,150 @@
       <c r="Z181" s="1"/>
       <c r="AA181" s="1"/>
     </row>
-    <row r="182" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
-      <c r="L182" s="6"/>
-      <c r="M182" s="6"/>
-      <c r="N182" s="6"/>
-      <c r="O182" s="6"/>
-      <c r="P182" s="6"/>
-      <c r="Q182" s="6"/>
-      <c r="R182" s="6"/>
-      <c r="S182" s="6"/>
-      <c r="T182" s="6"/>
-      <c r="U182" s="6"/>
-      <c r="V182" s="6"/>
-      <c r="W182" s="6"/>
-      <c r="X182" s="6"/>
-      <c r="Y182" s="6"/>
-      <c r="Z182" s="6"/>
-      <c r="AA182" s="6"/>
-    </row>
-    <row r="183" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
-      <c r="L183" s="6"/>
-      <c r="M183" s="6"/>
-      <c r="N183" s="6"/>
-      <c r="O183" s="6"/>
-      <c r="P183" s="6"/>
-      <c r="Q183" s="6"/>
-      <c r="R183" s="6"/>
-      <c r="S183" s="6"/>
-      <c r="T183" s="6"/>
-      <c r="U183" s="6"/>
-      <c r="V183" s="6"/>
-      <c r="W183" s="6"/>
-      <c r="X183" s="6"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="6"/>
-      <c r="AA183" s="6"/>
-    </row>
-    <row r="184" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-      <c r="J184" s="6"/>
-      <c r="K184" s="6"/>
-      <c r="L184" s="6"/>
-      <c r="M184" s="6"/>
-      <c r="N184" s="6"/>
-      <c r="O184" s="6"/>
-      <c r="P184" s="6"/>
-      <c r="Q184" s="6"/>
-      <c r="R184" s="6"/>
-      <c r="S184" s="6"/>
-      <c r="T184" s="6"/>
-      <c r="U184" s="6"/>
-      <c r="V184" s="6"/>
-      <c r="W184" s="6"/>
-      <c r="X184" s="6"/>
-      <c r="Y184" s="6"/>
-      <c r="Z184" s="6"/>
-      <c r="AA184" s="6"/>
-    </row>
-    <row r="185" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6"/>
-      <c r="M185" s="6"/>
-      <c r="N185" s="6"/>
-      <c r="O185" s="6"/>
-      <c r="P185" s="6"/>
-      <c r="Q185" s="6"/>
-      <c r="R185" s="6"/>
-      <c r="S185" s="6"/>
-      <c r="T185" s="6"/>
-      <c r="U185" s="6"/>
-      <c r="V185" s="6"/>
-      <c r="W185" s="6"/>
-      <c r="X185" s="6"/>
-      <c r="Y185" s="6"/>
-      <c r="Z185" s="6"/>
-      <c r="AA185" s="6"/>
-    </row>
-    <row r="186" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
-      <c r="M186" s="6"/>
-      <c r="N186" s="6"/>
-      <c r="O186" s="6"/>
-      <c r="P186" s="6"/>
-      <c r="Q186" s="6"/>
-      <c r="R186" s="6"/>
-      <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
-      <c r="X186" s="6"/>
-      <c r="Y186" s="6"/>
-      <c r="Z186" s="6"/>
-      <c r="AA186" s="6"/>
+    <row r="182" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="1"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="4"/>
+      <c r="G182" s="5"/>
+      <c r="H182" s="4"/>
+      <c r="I182" s="1"/>
+      <c r="J182" s="1"/>
+      <c r="K182" s="1"/>
+      <c r="L182" s="1"/>
+      <c r="M182" s="1"/>
+      <c r="N182" s="1"/>
+      <c r="O182" s="1"/>
+      <c r="P182" s="1"/>
+      <c r="Q182" s="1"/>
+      <c r="R182" s="1"/>
+      <c r="S182" s="1"/>
+      <c r="T182" s="1"/>
+      <c r="U182" s="1"/>
+      <c r="V182" s="1"/>
+      <c r="W182" s="1"/>
+      <c r="X182" s="1"/>
+      <c r="Y182" s="1"/>
+      <c r="Z182" s="1"/>
+      <c r="AA182" s="1"/>
+    </row>
+    <row r="183" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="1"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+      <c r="E183" s="1"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="5"/>
+      <c r="H183" s="4"/>
+      <c r="I183" s="1"/>
+      <c r="J183" s="1"/>
+      <c r="K183" s="1"/>
+      <c r="L183" s="1"/>
+      <c r="M183" s="1"/>
+      <c r="N183" s="1"/>
+      <c r="O183" s="1"/>
+      <c r="P183" s="1"/>
+      <c r="Q183" s="1"/>
+      <c r="R183" s="1"/>
+      <c r="S183" s="1"/>
+      <c r="T183" s="1"/>
+      <c r="U183" s="1"/>
+      <c r="V183" s="1"/>
+      <c r="W183" s="1"/>
+      <c r="X183" s="1"/>
+      <c r="Y183" s="1"/>
+      <c r="Z183" s="1"/>
+      <c r="AA183" s="1"/>
+    </row>
+    <row r="184" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="1"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="4"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="4"/>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
+      <c r="L184" s="1"/>
+      <c r="M184" s="1"/>
+      <c r="N184" s="1"/>
+      <c r="O184" s="1"/>
+      <c r="P184" s="1"/>
+      <c r="Q184" s="1"/>
+      <c r="R184" s="1"/>
+      <c r="S184" s="1"/>
+      <c r="T184" s="1"/>
+      <c r="U184" s="1"/>
+      <c r="V184" s="1"/>
+      <c r="W184" s="1"/>
+      <c r="X184" s="1"/>
+      <c r="Y184" s="1"/>
+      <c r="Z184" s="1"/>
+      <c r="AA184" s="1"/>
+    </row>
+    <row r="185" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="1"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+      <c r="E185" s="1"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="4"/>
+      <c r="I185" s="1"/>
+      <c r="J185" s="1"/>
+      <c r="K185" s="1"/>
+      <c r="L185" s="1"/>
+      <c r="M185" s="1"/>
+      <c r="N185" s="1"/>
+      <c r="O185" s="1"/>
+      <c r="P185" s="1"/>
+      <c r="Q185" s="1"/>
+      <c r="R185" s="1"/>
+      <c r="S185" s="1"/>
+      <c r="T185" s="1"/>
+      <c r="U185" s="1"/>
+      <c r="V185" s="1"/>
+      <c r="W185" s="1"/>
+      <c r="X185" s="1"/>
+      <c r="Y185" s="1"/>
+      <c r="Z185" s="1"/>
+      <c r="AA185" s="1"/>
+    </row>
+    <row r="186" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="1"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+      <c r="E186" s="1"/>
+      <c r="F186" s="4"/>
+      <c r="G186" s="5"/>
+      <c r="H186" s="4"/>
+      <c r="I186" s="1"/>
+      <c r="J186" s="1"/>
+      <c r="K186" s="1"/>
+      <c r="L186" s="1"/>
+      <c r="M186" s="1"/>
+      <c r="N186" s="1"/>
+      <c r="O186" s="1"/>
+      <c r="P186" s="1"/>
+      <c r="Q186" s="1"/>
+      <c r="R186" s="1"/>
+      <c r="S186" s="1"/>
+      <c r="T186" s="1"/>
+      <c r="U186" s="1"/>
+      <c r="V186" s="1"/>
+      <c r="W186" s="1"/>
+      <c r="X186" s="1"/>
+      <c r="Y186" s="1"/>
+      <c r="Z186" s="1"/>
+      <c r="AA186" s="1"/>
     </row>
     <row r="187" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
@@ -29548,20 +29469,223 @@
       <c r="Z955" s="6"/>
       <c r="AA955" s="6"/>
     </row>
+    <row r="956" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A956" s="6"/>
+      <c r="B956" s="6"/>
+      <c r="C956" s="6"/>
+      <c r="D956" s="6"/>
+      <c r="E956" s="6"/>
+      <c r="F956" s="6"/>
+      <c r="G956" s="6"/>
+      <c r="H956" s="6"/>
+      <c r="I956" s="6"/>
+      <c r="J956" s="6"/>
+      <c r="K956" s="6"/>
+      <c r="L956" s="6"/>
+      <c r="M956" s="6"/>
+      <c r="N956" s="6"/>
+      <c r="O956" s="6"/>
+      <c r="P956" s="6"/>
+      <c r="Q956" s="6"/>
+      <c r="R956" s="6"/>
+      <c r="S956" s="6"/>
+      <c r="T956" s="6"/>
+      <c r="U956" s="6"/>
+      <c r="V956" s="6"/>
+      <c r="W956" s="6"/>
+      <c r="X956" s="6"/>
+      <c r="Y956" s="6"/>
+      <c r="Z956" s="6"/>
+      <c r="AA956" s="6"/>
+    </row>
+    <row r="957" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A957" s="6"/>
+      <c r="B957" s="6"/>
+      <c r="C957" s="6"/>
+      <c r="D957" s="6"/>
+      <c r="E957" s="6"/>
+      <c r="F957" s="6"/>
+      <c r="G957" s="6"/>
+      <c r="H957" s="6"/>
+      <c r="I957" s="6"/>
+      <c r="J957" s="6"/>
+      <c r="K957" s="6"/>
+      <c r="L957" s="6"/>
+      <c r="M957" s="6"/>
+      <c r="N957" s="6"/>
+      <c r="O957" s="6"/>
+      <c r="P957" s="6"/>
+      <c r="Q957" s="6"/>
+      <c r="R957" s="6"/>
+      <c r="S957" s="6"/>
+      <c r="T957" s="6"/>
+      <c r="U957" s="6"/>
+      <c r="V957" s="6"/>
+      <c r="W957" s="6"/>
+      <c r="X957" s="6"/>
+      <c r="Y957" s="6"/>
+      <c r="Z957" s="6"/>
+      <c r="AA957" s="6"/>
+    </row>
+    <row r="958" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A958" s="6"/>
+      <c r="B958" s="6"/>
+      <c r="C958" s="6"/>
+      <c r="D958" s="6"/>
+      <c r="E958" s="6"/>
+      <c r="F958" s="6"/>
+      <c r="G958" s="6"/>
+      <c r="H958" s="6"/>
+      <c r="I958" s="6"/>
+      <c r="J958" s="6"/>
+      <c r="K958" s="6"/>
+      <c r="L958" s="6"/>
+      <c r="M958" s="6"/>
+      <c r="N958" s="6"/>
+      <c r="O958" s="6"/>
+      <c r="P958" s="6"/>
+      <c r="Q958" s="6"/>
+      <c r="R958" s="6"/>
+      <c r="S958" s="6"/>
+      <c r="T958" s="6"/>
+      <c r="U958" s="6"/>
+      <c r="V958" s="6"/>
+      <c r="W958" s="6"/>
+      <c r="X958" s="6"/>
+      <c r="Y958" s="6"/>
+      <c r="Z958" s="6"/>
+      <c r="AA958" s="6"/>
+    </row>
+    <row r="959" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A959" s="6"/>
+      <c r="B959" s="6"/>
+      <c r="C959" s="6"/>
+      <c r="D959" s="6"/>
+      <c r="E959" s="6"/>
+      <c r="F959" s="6"/>
+      <c r="G959" s="6"/>
+      <c r="H959" s="6"/>
+      <c r="I959" s="6"/>
+      <c r="J959" s="6"/>
+      <c r="K959" s="6"/>
+      <c r="L959" s="6"/>
+      <c r="M959" s="6"/>
+      <c r="N959" s="6"/>
+      <c r="O959" s="6"/>
+      <c r="P959" s="6"/>
+      <c r="Q959" s="6"/>
+      <c r="R959" s="6"/>
+      <c r="S959" s="6"/>
+      <c r="T959" s="6"/>
+      <c r="U959" s="6"/>
+      <c r="V959" s="6"/>
+      <c r="W959" s="6"/>
+      <c r="X959" s="6"/>
+      <c r="Y959" s="6"/>
+      <c r="Z959" s="6"/>
+      <c r="AA959" s="6"/>
+    </row>
+    <row r="960" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A960" s="6"/>
+      <c r="B960" s="6"/>
+      <c r="C960" s="6"/>
+      <c r="D960" s="6"/>
+      <c r="E960" s="6"/>
+      <c r="F960" s="6"/>
+      <c r="G960" s="6"/>
+      <c r="H960" s="6"/>
+      <c r="I960" s="6"/>
+      <c r="J960" s="6"/>
+      <c r="K960" s="6"/>
+      <c r="L960" s="6"/>
+      <c r="M960" s="6"/>
+      <c r="N960" s="6"/>
+      <c r="O960" s="6"/>
+      <c r="P960" s="6"/>
+      <c r="Q960" s="6"/>
+      <c r="R960" s="6"/>
+      <c r="S960" s="6"/>
+      <c r="T960" s="6"/>
+      <c r="U960" s="6"/>
+      <c r="V960" s="6"/>
+      <c r="W960" s="6"/>
+      <c r="X960" s="6"/>
+      <c r="Y960" s="6"/>
+      <c r="Z960" s="6"/>
+      <c r="AA960" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="90">
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J8"/>
+  <mergeCells count="95">
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B43:C44"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B45:C46"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B41:C42"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="A58:J59"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A25:C26"/>
+    <mergeCell ref="D25:F26"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A27:A42"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A7:B8"/>
     <mergeCell ref="C5:D6"/>
@@ -29575,73 +29699,20 @@
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A29:A34"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A27:C28"/>
-    <mergeCell ref="D27:F28"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A53:J54"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="G51:G52"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="A35:A41"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
-  <phoneticPr fontId="34" type="noConversion"/>
+  <phoneticPr fontId="33" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
+++ b/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\fic\chatgpt\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E1F070-5BDB-4168-A517-F191CCFCEF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9FED4E-598F-4BC5-838C-61A450AC0B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano de Ensino" sheetId="2" r:id="rId1"/>
+    <sheet name="Desafio01" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -204,9 +205,6 @@
     <t>1 Identificar inteligências artificiais generativas, suas arquiteturas e funcionamento.</t>
   </si>
   <si>
-    <t>Criar conta no GitHub, Instalar o ambiente de desenvolvimento composto por VsCode e Git for Windows. Criar um repositório e enviar uma página web simples.Colocar o repositório em produção com Git Pages.</t>
-  </si>
-  <si>
     <t>O que é uma IDE? Para que serve versionamento de sistemas? Quais as ferramentas mais comuns de versionamento? O que é Git? O que é github? Para que serve o VsCode?Quais os tipos de sistemas comerciais mais comuns atualmente? O que é SAS? O que é NLP? O que é visão computacional? O que são redes neurais?</t>
   </si>
   <si>
@@ -222,12 +220,6 @@
   </si>
   <si>
     <t>Dia03 Dia04 Dia05</t>
-  </si>
-  <si>
-    <t>8 Implementar o ChatGPT em aplicações de chatbot usando suas bibliotecas e APIs.
-2 Treinar IA , utilizando os fundamentos do aprendizado de máquina
-3 Criar um chatbot personalizado utilizando o processamento de linguagem natural (NLP)
-4 Estruturar e codificar solução utilizando inteligências artificiais</t>
   </si>
   <si>
     <t>Dia06 Dia07 Dia08 Dia09</t>
@@ -375,6 +367,93 @@
 [2 Demonstrar atenção aos detalhes.]</t>
     </r>
   </si>
+  <si>
+    <t>Situação Desafiadora: Conjectura de Collatz</t>
+  </si>
+  <si>
+    <t>Recebeu este nome em referência ao matemático alemão Lothar Collatz.</t>
+  </si>
+  <si>
+    <t>Contetualização:</t>
+  </si>
+  <si>
+    <t>A Conjectura de Collatz, ou problema, é um enigma matemático simples: para qualquer inteiro positivo, se par, divida por 2; se ímpar, multiplique por 3 e some 1. A conjectura afirma que, repetindo o processo, todos os números chegam ao ciclo que é 1.</t>
+  </si>
+  <si>
+    <t>Apesar de testada até números altíssimos, nunca foi provada.</t>
+  </si>
+  <si>
+    <t>Desafio:</t>
+  </si>
+  <si>
+    <t>Crie um programa que teste esta conjectura e informe quantos passos são necessários para chegar a 1, a partir de um número inteiro positivo informado pelo usuário.</t>
+  </si>
+  <si>
+    <t>O programa deve retornar o número de passos e a sequência de números gerada.</t>
+  </si>
+  <si>
+    <t>Pode escoher a linguagem de programação que desejar, não se preocupe com a beleza da UI (User Interface) neste momento.</t>
+  </si>
+  <si>
+    <t>Salve o programa em uma pasta em sua áre det trabalho, pois ele será versionado no git e enviado para o github.</t>
+  </si>
+  <si>
+    <t>Claro que pode contar com a ajuda de uma IA, como o ChatGPT, para ajudá-lo a desenvolver o programa.</t>
+  </si>
+  <si>
+    <t>Entrega:</t>
+  </si>
+  <si>
+    <t>O programa deve ser enviado para o github, e deixado como público, para que o instrutor e outros colegas possam acessar e aprender com o seu código.</t>
+  </si>
+  <si>
+    <t>2 Treinar IA , utilizando os fundamentos do aprendizado de máquina</t>
+  </si>
+  <si>
+    <t>3 Criar um chatbot personalizado utilizando o processamento de linguagem natural (NLP)</t>
+  </si>
+  <si>
+    <t>4 Estruturar e codificar solução utilizando inteligências artificiais</t>
+  </si>
+  <si>
+    <t>5 Corrigir erros em scripts, builds e deploys com ChatGPT.</t>
+  </si>
+  <si>
+    <t>6 Refatorar códigos com ChatGPT.</t>
+  </si>
+  <si>
+    <t>8 Implementar o ChatGPT em aplicações de chatbot usando suas bibliotecas e APIs.</t>
+  </si>
+  <si>
+    <t>1 Demonstração raciocínio lógico.</t>
+  </si>
+  <si>
+    <t>2 Demonstrar atenção aos detalhes.</t>
+  </si>
+  <si>
+    <t>Quais as tecologias de uma IA Generativa? O que são conjuntos de treinamento e avaliação? Quais as formas de utilização de IA para correção de códigos? Como o ChatGPT refatora códigos?</t>
+  </si>
+  <si>
+    <t>Exposição dialogada com emonstraçao, Solução de desafio com ajuda de IA generativa  e deixar púbico no GitHub Pages.</t>
+  </si>
+  <si>
+    <t>Exposição dialogda, Apesentação, Avaiação diagnóstica por entevista, Criar conta no GitHub, Instalar ambiente de desenvolvimento composto por VsCode e Git for Windows. Criar um repositório e enviar uma página web simples.Colocar o repositório em produção com Git Pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exposição dialogada, demonstrações, Pesquisa Web, Auxílio de IA, Solucionar a situação e aprendizagem:Chatbot com Gemini, Versionar e Publicar no Github Pages </t>
+  </si>
+  <si>
+    <t>Exposição dialogada, demonstrações, criação de um portifolio web público com pelo menos dois projetos concluídos ou em andamento.</t>
+  </si>
+  <si>
+    <t>O que é uma API? Como utilizar uma API? O que é uma chave de API? O que é refatoração de código? Como utilizar IA sem oncorer com ela? Como não deixar que a IA prejudique seu aprendizado? Quais conhecimentos agregam mais valor ao prendizado?</t>
+  </si>
+  <si>
+    <t>8 Implementar o ChatGPT em aplicações de chatbot usando suas bibliotecas e APIs.
+2 Treinar IA, utilizando os fundamentos do aprendizado de máquina
+3 Criar um chatbot personalizado utilizando o processamento de linguagem natural (NLP)
+4 Estruturar e codificar solução utilizando inteligências artificiais</t>
+  </si>
 </sst>
 </file>
 
@@ -384,7 +463,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,12 +631,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -615,22 +688,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -647,6 +704,54 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16.5"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.75"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1103,9 +1208,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1123,9 +1228,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1149,37 +1251,31 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1200,31 +1296,179 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1248,232 +1492,110 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1755,162 +1877,162 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="38" t="s">
+      <c r="B3" s="101"/>
+      <c r="C3" s="105" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="43" t="s">
+      <c r="D3" s="106"/>
+      <c r="E3" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="36" t="s">
+      <c r="F3" s="110"/>
+      <c r="G3" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36" t="s">
+      <c r="H3" s="103"/>
+      <c r="I3" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="36"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="47" t="s">
+      <c r="A4" s="100"/>
+      <c r="B4" s="101"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="51" t="s">
+      <c r="F4" s="99"/>
+      <c r="G4" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="51"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="57" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="66" t="s">
+      <c r="D5" s="85"/>
+      <c r="E5" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="67"/>
-      <c r="G5" s="51" t="s">
+      <c r="F5" s="93"/>
+      <c r="G5" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
+      <c r="J5" s="102"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="55"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="68" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="69"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="85"/>
+      <c r="J6" s="85"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="58" t="s">
+      <c r="B7" s="80"/>
+      <c r="C7" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="58"/>
-      <c r="E7" s="45" t="s">
+      <c r="D7" s="86"/>
+      <c r="E7" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
     </row>
     <row r="8" spans="1:27" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="59"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="60" t="s">
+      <c r="G10" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60" t="s">
+      <c r="H10" s="88"/>
+      <c r="I10" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="60"/>
+      <c r="J10" s="88"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1930,32 +2052,32 @@
       <c r="AA10" s="1"/>
     </row>
     <row r="11" spans="1:27" ht="255" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
-        <v>54</v>
+      <c r="A11" s="28" t="s">
+        <v>53</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="21">
         <v>8</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="107" t="s">
+      <c r="F11" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="64"/>
-      <c r="I11" s="61" t="s">
+      <c r="G11" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="62"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="90"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -1975,26 +2097,30 @@
       <c r="AA11" s="1"/>
     </row>
     <row r="12" spans="1:27" ht="132" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
-        <v>57</v>
+      <c r="A12" s="29" t="s">
+        <v>56</v>
       </c>
       <c r="B12" s="2">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
-      <c r="D12" s="33" t="s">
-        <v>61</v>
+      <c r="D12" s="30" t="s">
+        <v>59</v>
       </c>
-      <c r="E12" s="110" t="s">
-        <v>64</v>
+      <c r="E12" s="115" t="s">
+        <v>62</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="53"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="54"/>
+      <c r="I12" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="J12" s="82"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2014,24 +2140,28 @@
       <c r="AA12" s="3"/>
     </row>
     <row r="13" spans="1:27" ht="267.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>59</v>
+      <c r="A13" s="29" t="s">
+        <v>57</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>16</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>56</v>
+      <c r="C13" s="13" t="s">
+        <v>55</v>
       </c>
-      <c r="D13" s="33" t="s">
-        <v>62</v>
+      <c r="D13" s="30" t="s">
+        <v>60</v>
       </c>
-      <c r="E13" s="111"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="103"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="91" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="54"/>
+      <c r="I13" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="140"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2051,26 +2181,28 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="32" t="s">
-        <v>60</v>
+      <c r="A14" s="29" t="s">
+        <v>58</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>12</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>58</v>
+      <c r="C14" s="13" t="s">
+        <v>95</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>65</v>
+      <c r="F14" s="52"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="139" t="s">
+        <v>92</v>
       </c>
-      <c r="F14" s="109"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="103"/>
+      <c r="J14" s="140"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2090,21 +2222,21 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="26">
         <f>SUM(B8:B14)</f>
         <v>48</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="121"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="58"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2124,18 +2256,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="105"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="106"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2155,18 +2287,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="94" t="s">
-        <v>66</v>
+      <c r="A17" s="33" t="s">
+        <v>64</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="95"/>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="95"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2186,18 +2318,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="76.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="86" t="s">
-        <v>67</v>
+      <c r="A18" s="59" t="s">
+        <v>65</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="87"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2217,18 +2349,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
-      <c r="D19" s="95"/>
-      <c r="E19" s="95"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2248,18 +2380,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="116.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86" t="s">
-        <v>68</v>
+      <c r="A20" s="59" t="s">
+        <v>66</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="87"/>
-      <c r="G20" s="87"/>
-      <c r="H20" s="87"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="87"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2279,18 +2411,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="95" t="s">
+      <c r="A21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="95"/>
-      <c r="G21" s="95"/>
-      <c r="H21" s="95"/>
-      <c r="I21" s="95"/>
-      <c r="J21" s="95"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2310,18 +2442,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="228.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="86" t="s">
-        <v>69</v>
+      <c r="A22" s="59" t="s">
+        <v>67</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="86"/>
-      <c r="J22" s="86"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="59"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2341,16 +2473,16 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="93"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2370,18 +2502,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="99"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2401,22 +2533,22 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="88" t="s">
+      <c r="A25" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89"/>
-      <c r="D25" s="90" t="s">
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="100" t="s">
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2436,22 +2568,22 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A26" s="89"/>
-      <c r="B26" s="89"/>
-      <c r="C26" s="89"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="22">
+      <c r="A26" s="62"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="19">
         <v>1</v>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="19">
         <v>2</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="20">
         <v>3</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="20">
         <v>4</v>
       </c>
       <c r="K26" s="5"/>
@@ -2472,19 +2604,21 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="123"/>
-      <c r="C27" s="133"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
+      <c r="B27" s="117" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="120"/>
+      <c r="F27" s="121"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="124"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -2503,17 +2637,17 @@
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
     </row>
-    <row r="28" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="78"/>
-      <c r="B28" s="124"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
+      <c r="B28" s="125"/>
+      <c r="C28" s="126"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="120"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="127"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -2532,17 +2666,19 @@
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
     </row>
-    <row r="29" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="78"/>
-      <c r="B29" s="125"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="98"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
+      <c r="B29" s="128" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="129"/>
+      <c r="D29" s="130"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="123"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2561,17 +2697,17 @@
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="78"/>
-      <c r="B30" s="124"/>
-      <c r="C30" s="132"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="98"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
+      <c r="B30" s="125"/>
+      <c r="C30" s="126"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="123"/>
+      <c r="I30" s="127"/>
+      <c r="J30" s="127"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2590,17 +2726,19 @@
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
     </row>
-    <row r="31" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="78"/>
-      <c r="B31" s="125"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
+      <c r="B31" s="128" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="129"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="132"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="123"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="127"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -2619,17 +2757,17 @@
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
     </row>
-    <row r="32" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="78"/>
-      <c r="B32" s="124"/>
-      <c r="C32" s="132"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="98"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
+      <c r="B32" s="125"/>
+      <c r="C32" s="126"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="123"/>
+      <c r="I32" s="127"/>
+      <c r="J32" s="127"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -2648,17 +2786,19 @@
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
     </row>
-    <row r="33" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="78"/>
-      <c r="B33" s="125"/>
-      <c r="C33" s="131"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="98"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
+      <c r="B33" s="128" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="129"/>
+      <c r="D33" s="130"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="122"/>
+      <c r="H33" s="123"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="127"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2677,17 +2817,17 @@
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
     </row>
-    <row r="34" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
-      <c r="B34" s="124"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
+      <c r="B34" s="125"/>
+      <c r="C34" s="126"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="122"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="127"/>
+      <c r="J34" s="127"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2706,17 +2846,19 @@
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
     </row>
-    <row r="35" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
-      <c r="B35" s="125"/>
-      <c r="C35" s="131"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="98"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
+      <c r="B35" s="128" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="129"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="123"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2735,17 +2877,17 @@
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
     </row>
-    <row r="36" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="78"/>
-      <c r="B36" s="124"/>
-      <c r="C36" s="132"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="97"/>
-      <c r="F36" s="98"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
+      <c r="B36" s="125"/>
+      <c r="C36" s="126"/>
+      <c r="D36" s="130"/>
+      <c r="E36" s="131"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="123"/>
+      <c r="I36" s="127"/>
+      <c r="J36" s="127"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -2764,17 +2906,19 @@
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
     </row>
-    <row r="37" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="78"/>
-      <c r="B37" s="125"/>
-      <c r="C37" s="131"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+      <c r="B37" s="128" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="129"/>
+      <c r="D37" s="130"/>
+      <c r="E37" s="131"/>
+      <c r="F37" s="132"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="123"/>
+      <c r="I37" s="127"/>
+      <c r="J37" s="127"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2793,17 +2937,17 @@
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
     </row>
-    <row r="38" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="78"/>
-      <c r="B38" s="124"/>
-      <c r="C38" s="132"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="98"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+      <c r="B38" s="125"/>
+      <c r="C38" s="126"/>
+      <c r="D38" s="130"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="132"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="123"/>
+      <c r="I38" s="127"/>
+      <c r="J38" s="127"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2822,17 +2966,19 @@
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
     </row>
-    <row r="39" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
-      <c r="B39" s="125"/>
-      <c r="C39" s="131"/>
-      <c r="D39" s="96"/>
-      <c r="E39" s="97"/>
-      <c r="F39" s="98"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
+      <c r="B39" s="128" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="129"/>
+      <c r="D39" s="130"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="132"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="123"/>
+      <c r="I39" s="127"/>
+      <c r="J39" s="127"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2851,17 +2997,17 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
     </row>
-    <row r="40" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="78"/>
-      <c r="B40" s="124"/>
-      <c r="C40" s="132"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="97"/>
-      <c r="F40" s="98"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
+      <c r="B40" s="125"/>
+      <c r="C40" s="126"/>
+      <c r="D40" s="130"/>
+      <c r="E40" s="131"/>
+      <c r="F40" s="132"/>
+      <c r="G40" s="122"/>
+      <c r="H40" s="123"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="127"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2880,17 +3026,19 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
     </row>
-    <row r="41" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="78"/>
-      <c r="B41" s="125"/>
-      <c r="C41" s="131"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="97"/>
-      <c r="F41" s="98"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
+      <c r="B41" s="128" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="129"/>
+      <c r="D41" s="130"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="132"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="127"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -2909,17 +3057,17 @@
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
     </row>
-    <row r="42" spans="1:27" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="78"/>
-      <c r="B42" s="124"/>
-      <c r="C42" s="132"/>
-      <c r="D42" s="96"/>
-      <c r="E42" s="97"/>
-      <c r="F42" s="98"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
+      <c r="B42" s="125"/>
+      <c r="C42" s="126"/>
+      <c r="D42" s="130"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="132"/>
+      <c r="G42" s="122"/>
+      <c r="H42" s="123"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="127"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -2938,17 +3086,19 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
     </row>
-    <row r="43" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="122"/>
-      <c r="B43" s="123"/>
-      <c r="C43" s="133"/>
-      <c r="D43" s="129"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="130"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
+    <row r="43" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="35"/>
+      <c r="B43" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="118"/>
+      <c r="D43" s="133"/>
+      <c r="E43" s="134"/>
+      <c r="F43" s="135"/>
+      <c r="G43" s="122"/>
+      <c r="H43" s="123"/>
+      <c r="I43" s="127"/>
+      <c r="J43" s="127"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2967,17 +3117,17 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
     </row>
-    <row r="44" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="122"/>
-      <c r="B44" s="124"/>
-      <c r="C44" s="132"/>
-      <c r="D44" s="126"/>
-      <c r="E44" s="127"/>
-      <c r="F44" s="128"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
+    <row r="44" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="35"/>
+      <c r="B44" s="125"/>
+      <c r="C44" s="126"/>
+      <c r="D44" s="136"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="122"/>
+      <c r="H44" s="123"/>
+      <c r="I44" s="127"/>
+      <c r="J44" s="127"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -2996,17 +3146,19 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
     </row>
-    <row r="45" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="122"/>
-      <c r="B45" s="125"/>
-      <c r="C45" s="131"/>
-      <c r="D45" s="129"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="130"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
+    <row r="45" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+      <c r="B45" s="128" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="129"/>
+      <c r="D45" s="133"/>
+      <c r="E45" s="134"/>
+      <c r="F45" s="135"/>
+      <c r="G45" s="122"/>
+      <c r="H45" s="123"/>
+      <c r="I45" s="127"/>
+      <c r="J45" s="127"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -3025,17 +3177,17 @@
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
     </row>
-    <row r="46" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="122"/>
-      <c r="B46" s="124"/>
-      <c r="C46" s="132"/>
-      <c r="D46" s="126"/>
-      <c r="E46" s="127"/>
-      <c r="F46" s="128"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
+    <row r="46" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="35"/>
+      <c r="B46" s="125"/>
+      <c r="C46" s="126"/>
+      <c r="D46" s="136"/>
+      <c r="E46" s="137"/>
+      <c r="F46" s="138"/>
+      <c r="G46" s="122"/>
+      <c r="H46" s="123"/>
+      <c r="I46" s="127"/>
+      <c r="J46" s="127"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -3055,14 +3207,14 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="74"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
+      <c r="A47" s="75"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="76"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3084,18 +3236,18 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="70" t="s">
+      <c r="A48" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="71"/>
-      <c r="C48" s="71"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="73" t="s">
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="71"/>
-      <c r="H48" s="72"/>
+      <c r="G48" s="72"/>
+      <c r="H48" s="73"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3117,20 +3269,20 @@
       <c r="AA48" s="1"/>
     </row>
     <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
+      <c r="A49" s="7">
         <v>5</v>
       </c>
-      <c r="B49" s="84" t="s">
+      <c r="B49" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="81"/>
-      <c r="D49" s="81"/>
-      <c r="E49" s="82"/>
-      <c r="F49" s="83">
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="40">
         <v>100</v>
       </c>
-      <c r="G49" s="81"/>
-      <c r="H49" s="82"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="39"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -3152,20 +3304,20 @@
       <c r="AA49" s="1"/>
     </row>
     <row r="50" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8">
+      <c r="A50" s="7">
         <v>4</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="81"/>
-      <c r="D50" s="81"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="83">
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="40">
         <v>80</v>
       </c>
-      <c r="G50" s="81"/>
-      <c r="H50" s="82"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="39"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3187,20 +3339,20 @@
       <c r="AA50" s="1"/>
     </row>
     <row r="51" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+      <c r="A51" s="7">
         <v>3</v>
       </c>
-      <c r="B51" s="85" t="s">
+      <c r="B51" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="81"/>
-      <c r="D51" s="81"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="83">
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="40">
         <v>65</v>
       </c>
-      <c r="G51" s="81"/>
-      <c r="H51" s="82"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="39"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3222,20 +3374,20 @@
       <c r="AA51" s="1"/>
     </row>
     <row r="52" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
+      <c r="A52" s="7">
         <v>2</v>
       </c>
-      <c r="B52" s="80" t="s">
+      <c r="B52" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="83">
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="40">
         <v>50</v>
       </c>
-      <c r="G52" s="81"/>
-      <c r="H52" s="82"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="39"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3257,20 +3409,20 @@
       <c r="AA52" s="1"/>
     </row>
     <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
+      <c r="A53" s="7">
         <v>1</v>
       </c>
-      <c r="B53" s="84" t="s">
+      <c r="B53" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="81"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="82"/>
-      <c r="F53" s="83">
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="40">
         <v>30</v>
       </c>
-      <c r="G53" s="81"/>
-      <c r="H53" s="82"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="39"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -3292,14 +3444,14 @@
       <c r="AA53" s="1"/>
     </row>
     <row r="54" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -3321,20 +3473,20 @@
       <c r="AA54" s="1"/>
     </row>
     <row r="55" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="17" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3356,22 +3508,22 @@
       <c r="AA55" s="1"/>
     </row>
     <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="18" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="113">
+      <c r="E56" s="41">
         <v>1</v>
       </c>
-      <c r="F56" s="113">
+      <c r="F56" s="41">
         <v>0</v>
       </c>
-      <c r="G56" s="101" t="s">
+      <c r="G56" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="116" t="s">
+      <c r="H56" s="45" t="s">
         <v>22</v>
       </c>
       <c r="I56" s="1"/>
@@ -3395,16 +3547,16 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="27" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="114"/>
-      <c r="F57" s="114"/>
-      <c r="G57" s="115"/>
-      <c r="H57" s="117"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="46"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -3426,18 +3578,18 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="112" t="s">
+      <c r="A58" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="112"/>
-      <c r="C58" s="112"/>
-      <c r="D58" s="112"/>
-      <c r="E58" s="112"/>
-      <c r="F58" s="112"/>
-      <c r="G58" s="112"/>
-      <c r="H58" s="112"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="112"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="36"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="36"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3457,16 +3609,16 @@
       <c r="AA58" s="1"/>
     </row>
     <row r="59" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="112"/>
-      <c r="B59" s="112"/>
-      <c r="C59" s="112"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="112"/>
-      <c r="H59" s="112"/>
-      <c r="I59" s="112"/>
-      <c r="J59" s="112"/>
+      <c r="A59" s="36"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
+      <c r="H59" s="36"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="36"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -29616,21 +29768,64 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A21:J21"/>
-    <mergeCell ref="B27:C28"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A27:A42"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A58:J59"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
     <mergeCell ref="A43:A46"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="B43:C44"/>
@@ -29641,22 +29836,13 @@
     <mergeCell ref="B41:C42"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="A58:J59"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="B27:C28"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A25:C26"/>
     <mergeCell ref="D25:F26"/>
@@ -29666,53 +29852,22 @@
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="G25:J25"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="B33:C34"/>
     <mergeCell ref="B31:C32"/>
     <mergeCell ref="D31:F31"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A27:A42"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J8"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E3:F3"/>
   </mergeCells>
-  <phoneticPr fontId="33" type="noConversion"/>
+  <phoneticPr fontId="32" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I12:J12" location="Desafio01!A1" display="Solucionar um desafio com ajuda de uma IA generativa  e deixar púbico no GitHub Pages." xr:uid="{C34EA30B-E5B1-4472-B11D-DD22B093A071}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -29721,4 +29876,82 @@
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C542F3E4-A663-432A-A023-F3484512F4E7}">
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="90.09765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="111" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="112" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A3" s="113" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="112" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="114" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A6" s="113" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="114" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="114" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="114" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="114" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="114" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A12" s="113" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="114" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
+++ b/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\fic\chatgpt\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9FED4E-598F-4BC5-838C-61A450AC0B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F2542B-4A03-4894-B029-7ED9CB904E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plano de Ensino" sheetId="2" r:id="rId1"/>
     <sheet name="Desafio01" sheetId="3" r:id="rId2"/>
+    <sheet name="PortFolio" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -454,6 +455,69 @@
 3 Criar um chatbot personalizado utilizando o processamento de linguagem natural (NLP)
 4 Estruturar e codificar solução utilizando inteligências artificiais</t>
   </si>
+  <si>
+    <t>Antes de iniciar nosso portifólio, vamos dsenvolvr alguns projetos com a ajuda de IA como ChatGPT, para que possamos ter projetos para incluir em nosso portifólio.</t>
+  </si>
+  <si>
+    <t>Projetos:</t>
+  </si>
+  <si>
+    <t>Segue algumas sujestões de temas baseados no portifolio do instrutor e de outros profissionais da área, para que possam se inspirar e desenvolver seus projetos:</t>
+  </si>
+  <si>
+    <t>Site de pedidos e entregas para um restaurante, utilizando [HTML], [CSS] e [JavaScript].</t>
+  </si>
+  <si>
+    <t>Jogo da memória utilizando [HTML], [CSS] e [JavaScript].</t>
+  </si>
+  <si>
+    <t>Jogo da velha utilizando [HTML], [CSS] e [JavaScript].</t>
+  </si>
+  <si>
+    <t>Simulador de investimentos a longo prazo utilizando [HTML], [CSS] e [JavaScript] consumindo API que disponibilize CDI atual.</t>
+  </si>
+  <si>
+    <t>Jogo Termo utilizando [HTML], [CSS] e [JavaScript].</t>
+  </si>
+  <si>
+    <t>Jogo pedra, papel e tesoura utilizando [HTML], [CSS] e [JavaScript].</t>
+  </si>
+  <si>
+    <t>Livro de receitas utilizando [HTML], [CSS] e [JavaScript] e Firebase para armazenamento de dados.</t>
+  </si>
+  <si>
+    <t>Missão</t>
+  </si>
+  <si>
+    <t>Vamos escolher dois projetos para desenvolver, utilizando as tecnologias que você domina ou deseja aprender. Utilize o ChatGPT para te ajudar a desenvolver os projetos, seja para gerar código, corrigir erros, refatorar códigos, aprender novas tecnologias, entre outros.</t>
+  </si>
+  <si>
+    <t>Caso sobre tempo, podemos desenvolver mais projetos, ou aprimorar os projetos desenvolvidos, utilizando as ferramentas de IA para aumentar a produtividade e qualidade do código.</t>
+  </si>
+  <si>
+    <t>Atividade prática: Portifólio</t>
+  </si>
+  <si>
+    <t>Contextualização:</t>
+  </si>
+  <si>
+    <t>O portifólio é uma ferramenta importante para apresentar suas habilidades e projetos para futuros empregadores, clientes ou parceiros. Ele pode ser utilizado para mostrar seus projetos pessoais, trabalhos acadêmicos, contribuições para projetos de código aberto, entre outros.</t>
+  </si>
+  <si>
+    <t>Crie um portifólio online utilizando uma plataforma de sua escolha, como GitHub Pages, WordPress, Wix, entre outros.</t>
+  </si>
+  <si>
+    <t>O portifólio deve conter uma seção de projetos, onde você deve incluir pelo menos 2 projetos que você desenvolveu, seja para fins acadêmicos, pessoais ou profissionais. Para cada projeto, inclua uma descrição do projeto, as tecnologias utilizadas e um link para o código-fonte (se disponível).</t>
+  </si>
+  <si>
+    <t>O portifólio deve conter uma seção de habilidades, onde você deve listar as tecnologias que você domina, como linguagens de programação, bibliotecas, frameworks, entre outros.</t>
+  </si>
+  <si>
+    <t>O portifólio deve ser enviado para o github, e deixado como público, para que o instrutor e outros colegas possam acessar e aprender com o seu código.</t>
+  </si>
+  <si>
+    <t>Habilite o GitHub Pages para o seu repositório, para que o portifólio possa ser acessado através de um link personalizado.</t>
+  </si>
 </sst>
 </file>
 
@@ -463,7 +527,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="45" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,6 +819,24 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="19.25"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16.5"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1210,7 +1292,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1296,19 +1378,159 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1316,20 +1538,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1350,10 +1568,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1367,6 +1588,67 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1398,204 +1680,28 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1877,134 +1983,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="100" t="s">
+      <c r="A3" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="105" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="106"/>
-      <c r="E3" s="109" t="s">
+      <c r="D3" s="44"/>
+      <c r="E3" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="110"/>
-      <c r="G3" s="103" t="s">
+      <c r="F3" s="49"/>
+      <c r="G3" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103" t="s">
+      <c r="H3" s="42"/>
+      <c r="I3" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="103"/>
+      <c r="J3" s="42"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="98" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="99"/>
-      <c r="G4" s="102" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="102"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="84" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="63" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="85"/>
-      <c r="E5" s="92" t="s">
+      <c r="D5" s="47"/>
+      <c r="E5" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="102" t="s">
+      <c r="F5" s="67"/>
+      <c r="G5" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="80"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="94" t="s">
+      <c r="A6" s="61"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="86" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="86"/>
-      <c r="E7" s="96" t="s">
+      <c r="D7" s="64"/>
+      <c r="E7" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="97"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:27" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
-      <c r="B8" s="79"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="85"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
@@ -2025,14 +2131,14 @@
       <c r="F10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="88" t="s">
+      <c r="G10" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88" t="s">
+      <c r="H10" s="55"/>
+      <c r="I10" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="88"/>
+      <c r="J10" s="55"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2067,17 +2173,17 @@
       <c r="E11" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="91" t="s">
+      <c r="G11" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="54"/>
-      <c r="I11" s="89" t="s">
+      <c r="H11" s="59"/>
+      <c r="I11" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="90"/>
+      <c r="J11" s="57"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2109,18 +2215,18 @@
       <c r="D12" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="115" t="s">
+      <c r="E12" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="91" t="s">
+      <c r="F12" s="101"/>
+      <c r="G12" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="54"/>
-      <c r="I12" s="81" t="s">
+      <c r="H12" s="59"/>
+      <c r="I12" s="110" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="82"/>
+      <c r="J12" s="111"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2152,16 +2258,16 @@
       <c r="D13" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="116"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="91" t="s">
+      <c r="E13" s="104"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="54"/>
-      <c r="I13" s="139" t="s">
+      <c r="H13" s="59"/>
+      <c r="I13" s="147" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="140"/>
+      <c r="J13" s="148"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2196,13 +2302,13 @@
       <c r="E14" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="139" t="s">
+      <c r="F14" s="102"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="95" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="140"/>
+      <c r="J14" s="96"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2233,10 +2339,10 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="58"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="109"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2256,18 +2362,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="49"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2287,18 +2393,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+      <c r="A17" s="129" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2318,18 +2424,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="76.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="131" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="132"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="132"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2349,18 +2455,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
+      <c r="J19" s="130"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2380,18 +2486,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="116.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="131" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
+      <c r="B20" s="132"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="132"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="132"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2411,18 +2517,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="130" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="130"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2442,18 +2548,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="228.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2473,16 +2579,16 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
+      <c r="A23" s="136"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="138"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2502,18 +2608,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="139" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="67"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="67"/>
+      <c r="B24" s="139"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="139"/>
+      <c r="I24" s="139"/>
+      <c r="J24" s="139"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2533,22 +2639,22 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="63" t="s">
+      <c r="B25" s="134"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="68" t="s">
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="115"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2568,12 +2674,12 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A26" s="62"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
       <c r="G26" s="19">
         <v>1</v>
       </c>
@@ -2605,20 +2711,20 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="121"/>
-      <c r="G27" s="122"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="124"/>
+      <c r="C27" s="121"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -2638,16 +2744,16 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="78"/>
-      <c r="B28" s="125"/>
-      <c r="C28" s="126"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="121"/>
-      <c r="G28" s="122"/>
-      <c r="H28" s="123"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="127"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -2667,18 +2773,18 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="78"/>
-      <c r="B29" s="128" t="s">
+      <c r="A29" s="85"/>
+      <c r="B29" s="127" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="123"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2698,16 +2804,16 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="78"/>
-      <c r="B30" s="125"/>
-      <c r="C30" s="126"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="132"/>
-      <c r="G30" s="122"/>
-      <c r="H30" s="123"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
+      <c r="A30" s="85"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2727,18 +2833,18 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="78"/>
-      <c r="B31" s="128" t="s">
+      <c r="A31" s="85"/>
+      <c r="B31" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="129"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="132"/>
-      <c r="G31" s="122"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="127"/>
+      <c r="C31" s="128"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -2758,16 +2864,16 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="78"/>
-      <c r="B32" s="125"/>
-      <c r="C32" s="126"/>
-      <c r="D32" s="130"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="122"/>
-      <c r="H32" s="123"/>
-      <c r="I32" s="127"/>
-      <c r="J32" s="127"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="122"/>
+      <c r="C32" s="123"/>
+      <c r="D32" s="78"/>
+      <c r="E32" s="79"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -2787,18 +2893,18 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="78"/>
-      <c r="B33" s="128" t="s">
+      <c r="A33" s="85"/>
+      <c r="B33" s="127" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="129"/>
-      <c r="D33" s="130"/>
-      <c r="E33" s="131"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="122"/>
-      <c r="H33" s="123"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
+      <c r="C33" s="128"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2818,16 +2924,16 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="78"/>
-      <c r="B34" s="125"/>
-      <c r="C34" s="126"/>
-      <c r="D34" s="130"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="132"/>
-      <c r="G34" s="122"/>
-      <c r="H34" s="123"/>
-      <c r="I34" s="127"/>
-      <c r="J34" s="127"/>
+      <c r="A34" s="85"/>
+      <c r="B34" s="122"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2847,18 +2953,18 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="78"/>
-      <c r="B35" s="128" t="s">
+      <c r="A35" s="85"/>
+      <c r="B35" s="127" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="129"/>
-      <c r="D35" s="130"/>
-      <c r="E35" s="131"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="122"/>
-      <c r="H35" s="123"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127"/>
+      <c r="C35" s="128"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2878,16 +2984,16 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="78"/>
-      <c r="B36" s="125"/>
-      <c r="C36" s="126"/>
-      <c r="D36" s="130"/>
-      <c r="E36" s="131"/>
-      <c r="F36" s="132"/>
-      <c r="G36" s="122"/>
-      <c r="H36" s="123"/>
-      <c r="I36" s="127"/>
-      <c r="J36" s="127"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="122"/>
+      <c r="C36" s="123"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -2907,18 +3013,18 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="78"/>
-      <c r="B37" s="128" t="s">
+      <c r="A37" s="85"/>
+      <c r="B37" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="129"/>
-      <c r="D37" s="130"/>
-      <c r="E37" s="131"/>
-      <c r="F37" s="132"/>
-      <c r="G37" s="122"/>
-      <c r="H37" s="123"/>
-      <c r="I37" s="127"/>
-      <c r="J37" s="127"/>
+      <c r="C37" s="128"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2938,16 +3044,16 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="78"/>
-      <c r="B38" s="125"/>
-      <c r="C38" s="126"/>
-      <c r="D38" s="130"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="132"/>
-      <c r="G38" s="122"/>
-      <c r="H38" s="123"/>
-      <c r="I38" s="127"/>
-      <c r="J38" s="127"/>
+      <c r="A38" s="85"/>
+      <c r="B38" s="122"/>
+      <c r="C38" s="123"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2967,18 +3073,18 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="78"/>
-      <c r="B39" s="128" t="s">
+      <c r="A39" s="85"/>
+      <c r="B39" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="129"/>
-      <c r="D39" s="130"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="132"/>
-      <c r="G39" s="122"/>
-      <c r="H39" s="123"/>
-      <c r="I39" s="127"/>
-      <c r="J39" s="127"/>
+      <c r="C39" s="128"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2998,16 +3104,16 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="78"/>
-      <c r="B40" s="125"/>
-      <c r="C40" s="126"/>
-      <c r="D40" s="130"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="132"/>
-      <c r="G40" s="122"/>
-      <c r="H40" s="123"/>
-      <c r="I40" s="127"/>
-      <c r="J40" s="127"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="122"/>
+      <c r="C40" s="123"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -3027,18 +3133,18 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="78"/>
-      <c r="B41" s="128" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="129"/>
-      <c r="D41" s="130"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="132"/>
-      <c r="G41" s="122"/>
-      <c r="H41" s="123"/>
-      <c r="I41" s="127"/>
-      <c r="J41" s="127"/>
+      <c r="C41" s="128"/>
+      <c r="D41" s="78"/>
+      <c r="E41" s="79"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -3058,16 +3164,16 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="78"/>
-      <c r="B42" s="125"/>
-      <c r="C42" s="126"/>
-      <c r="D42" s="130"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="132"/>
-      <c r="G42" s="122"/>
-      <c r="H42" s="123"/>
-      <c r="I42" s="127"/>
-      <c r="J42" s="127"/>
+      <c r="A42" s="85"/>
+      <c r="B42" s="122"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="79"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -3087,18 +3193,18 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="35"/>
-      <c r="B43" s="117" t="s">
+      <c r="A43" s="119"/>
+      <c r="B43" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="118"/>
-      <c r="D43" s="133"/>
-      <c r="E43" s="134"/>
-      <c r="F43" s="135"/>
-      <c r="G43" s="122"/>
-      <c r="H43" s="123"/>
-      <c r="I43" s="127"/>
-      <c r="J43" s="127"/>
+      <c r="C43" s="121"/>
+      <c r="D43" s="124"/>
+      <c r="E43" s="125"/>
+      <c r="F43" s="126"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -3118,16 +3224,16 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="126"/>
-      <c r="D44" s="136"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="122"/>
-      <c r="H44" s="123"/>
-      <c r="I44" s="127"/>
-      <c r="J44" s="127"/>
+      <c r="A44" s="119"/>
+      <c r="B44" s="122"/>
+      <c r="C44" s="123"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="82"/>
+      <c r="F44" s="83"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="40"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -3147,18 +3253,18 @@
       <c r="AA44" s="1"/>
     </row>
     <row r="45" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="35"/>
-      <c r="B45" s="128" t="s">
+      <c r="A45" s="119"/>
+      <c r="B45" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="C45" s="129"/>
-      <c r="D45" s="133"/>
-      <c r="E45" s="134"/>
-      <c r="F45" s="135"/>
-      <c r="G45" s="122"/>
-      <c r="H45" s="123"/>
-      <c r="I45" s="127"/>
-      <c r="J45" s="127"/>
+      <c r="C45" s="128"/>
+      <c r="D45" s="124"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="40"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -3178,16 +3284,16 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="35"/>
-      <c r="B46" s="125"/>
-      <c r="C46" s="126"/>
-      <c r="D46" s="136"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="122"/>
-      <c r="H46" s="123"/>
-      <c r="I46" s="127"/>
-      <c r="J46" s="127"/>
+      <c r="A46" s="119"/>
+      <c r="B46" s="122"/>
+      <c r="C46" s="123"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="40"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -3207,14 +3313,14 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="75"/>
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="76"/>
+      <c r="A47" s="76"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
+      <c r="F47" s="77"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="77"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3236,18 +3342,18 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="71" t="s">
+      <c r="A48" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
-      <c r="D48" s="72"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="74" t="s">
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="72"/>
-      <c r="H48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="74"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3272,17 +3378,17 @@
       <c r="A49" s="7">
         <v>5</v>
       </c>
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="40">
+      <c r="C49" s="90"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="91"/>
+      <c r="F49" s="92">
         <v>100</v>
       </c>
-      <c r="G49" s="38"/>
-      <c r="H49" s="39"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="91"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -3307,17 +3413,17 @@
       <c r="A50" s="7">
         <v>4</v>
       </c>
-      <c r="B50" s="70" t="s">
+      <c r="B50" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="40">
+      <c r="C50" s="90"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="91"/>
+      <c r="F50" s="92">
         <v>80</v>
       </c>
-      <c r="G50" s="38"/>
-      <c r="H50" s="39"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="91"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3342,17 +3448,17 @@
       <c r="A51" s="7">
         <v>3</v>
       </c>
-      <c r="B51" s="70" t="s">
+      <c r="B51" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="40">
+      <c r="C51" s="90"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="91"/>
+      <c r="F51" s="92">
         <v>65</v>
       </c>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
+      <c r="G51" s="90"/>
+      <c r="H51" s="91"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3377,17 +3483,17 @@
       <c r="A52" s="7">
         <v>2</v>
       </c>
-      <c r="B52" s="69" t="s">
+      <c r="B52" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="40">
+      <c r="C52" s="90"/>
+      <c r="D52" s="90"/>
+      <c r="E52" s="91"/>
+      <c r="F52" s="92">
         <v>50</v>
       </c>
-      <c r="G52" s="38"/>
-      <c r="H52" s="39"/>
+      <c r="G52" s="90"/>
+      <c r="H52" s="91"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3412,17 +3518,17 @@
       <c r="A53" s="7">
         <v>1</v>
       </c>
-      <c r="B53" s="37" t="s">
+      <c r="B53" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="40">
+      <c r="C53" s="90"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="92">
         <v>30</v>
       </c>
-      <c r="G53" s="38"/>
-      <c r="H53" s="39"/>
+      <c r="G53" s="90"/>
+      <c r="H53" s="91"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -3514,16 +3620,16 @@
       <c r="D56" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="41">
+      <c r="E56" s="113">
         <v>1</v>
       </c>
-      <c r="F56" s="41">
+      <c r="F56" s="113">
         <v>0</v>
       </c>
-      <c r="G56" s="43" t="s">
+      <c r="G56" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="45" t="s">
+      <c r="H56" s="117" t="s">
         <v>22</v>
       </c>
       <c r="I56" s="1"/>
@@ -3553,10 +3659,10 @@
       <c r="D57" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="46"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="116"/>
+      <c r="H57" s="118"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -3578,18 +3684,18 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="36" t="s">
+      <c r="A58" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="B58" s="36"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="36"/>
+      <c r="B58" s="112"/>
+      <c r="C58" s="112"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="112"/>
+      <c r="H58" s="112"/>
+      <c r="I58" s="112"/>
+      <c r="J58" s="112"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3609,16 +3715,16 @@
       <c r="AA58" s="1"/>
     </row>
     <row r="59" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="36"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="36"/>
+      <c r="A59" s="112"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="112"/>
+      <c r="D59" s="112"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="112"/>
+      <c r="G59" s="112"/>
+      <c r="H59" s="112"/>
+      <c r="I59" s="112"/>
+      <c r="J59" s="112"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -29768,71 +29874,20 @@
     </row>
   </sheetData>
   <mergeCells count="95">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J8"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A27:A42"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A58:J59"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B43:C44"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B45:C46"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="B41:C42"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
@@ -29849,24 +29904,76 @@
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A58:J59"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A27:A42"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B43:C44"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B45:C46"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <phoneticPr fontId="32" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I12:J12" location="Desafio01!A1" display="Solucionar um desafio com ajuda de uma IA generativa  e deixar púbico no GitHub Pages." xr:uid="{C34EA30B-E5B1-4472-B11D-DD22B093A071}"/>
+    <hyperlink ref="I13:J13" location="PortFolio!A1" display="Exposição dialogada, demonstrações, criação de um portifolio web público com pelo menos dois projetos concluídos ou em andamento." xr:uid="{07706612-ED63-4036-B091-EDE307D89F89}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29883,75 +29990,211 @@
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="90.09765625" customWidth="1"/>
+    <col min="1" max="1" width="94.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="33" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="34" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="35" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="112" t="s">
+      <c r="A4" s="34" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="36" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="35" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="114" t="s">
+      <c r="A7" s="36" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="114" t="s">
+      <c r="A8" s="36" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="114" t="s">
+      <c r="A9" s="36" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="114" t="s">
+      <c r="A10" s="36" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="114" t="s">
+      <c r="A11" s="36" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="35" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="36" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2792ACE-7C85-44AD-80D6-0C118606B812}">
+  <dimension ref="A1:A30"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="98.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="141" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="142" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="143" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="145" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="145" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="145" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="145" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="145" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="144" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="144" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="142" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="144" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="144" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="142" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="146" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="141" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="146" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="144" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="144" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="144" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="146" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="144" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="144" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" display="https://wellifabio.github.io/" xr:uid="{FE920721-00C2-4563-B96A-204D0243F275}"/>
+    <hyperlink ref="A5" r:id="rId2" display="https://wellifabio.github.io/delivery/delivery.html" xr:uid="{0E7DBEBC-3972-4CF2-AFA6-472827E59BD2}"/>
+    <hyperlink ref="A6" r:id="rId3" display="https://wellifabio.github.io/memoria/" xr:uid="{F7ACFA47-88B4-4AC9-BC06-D045D6B24C20}"/>
+    <hyperlink ref="A7" r:id="rId4" display="https://wellifabio.github.io/hash/" xr:uid="{BCDEF73E-1614-461F-877D-D3CADC8C5EA7}"/>
+    <hyperlink ref="A8" r:id="rId5" display="https://wellifabio.github.io/siminvest/" xr:uid="{CE7322C9-7B68-4922-99DE-EC9A3A8523E3}"/>
+    <hyperlink ref="A9" r:id="rId6" display="https://wellifabio.github.io/termo/" xr:uid="{48EF8DBF-306A-467B-88D6-E32A8FA139B4}"/>
+  </hyperlinks>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
+++ b/fic/chatgpt/planos/plano_ensino_chatgpt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\fic\chatgpt\planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F2542B-4A03-4894-B029-7ED9CB904E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216DD663-05BC-4A87-B193-D7B0A2E80C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="141">
   <si>
     <t>PLANO DE ENSINO</t>
   </si>
@@ -150,12 +150,6 @@
   </si>
   <si>
     <t>Carga Horária Não-Presencial: 0</t>
-  </si>
-  <si>
-    <t>Acertou todos os critérios críticos e pelo menos 1 dos 4 desejáveis</t>
-  </si>
-  <si>
-    <t>Acertou todos os critérios críticos e pelo menos 2 dos 4 desejáveis</t>
   </si>
   <si>
     <t>Avaliação Formativa - Situação Problema</t>
@@ -518,6 +512,84 @@
   <si>
     <t>Habilite o GitHub Pages para o seu repositório, para que o portifólio possa ser acessado através de um link personalizado.</t>
   </si>
+  <si>
+    <t>Desenvoleu as funcionalidades básicas do chatbot com auxílio do instrutor e IA</t>
+  </si>
+  <si>
+    <t>Utilzou a ia como apoio a produtividade e não como protagonista</t>
+  </si>
+  <si>
+    <t>Contruiu prompt com as confiurações para que a IA responda de acordo com o tema ecolhido</t>
+  </si>
+  <si>
+    <t>Definiu diretrizes de persolaidade de acordo com o tema</t>
+  </si>
+  <si>
+    <t>Entregou o projeto conforme orientado</t>
+  </si>
+  <si>
+    <t>Habilitou o Girhub Pages e adicionou ao portifolio</t>
+  </si>
+  <si>
+    <t>Conectou uma API de IA Gemini ou outra ao projeto</t>
+  </si>
+  <si>
+    <t>Criou a UI(User interface) com padrão de palheta de cores e acessibilidade visual mínima</t>
+  </si>
+  <si>
+    <t>Utilizou a IA para corrigir erros e auxiliar na implantação</t>
+  </si>
+  <si>
+    <t>Entregou o projeto funicionando corretamente</t>
+  </si>
+  <si>
+    <t>Deixou o código limpo</t>
+  </si>
+  <si>
+    <t>Treinou a IA de cordo com o tema escolhido</t>
+  </si>
+  <si>
+    <t>Removeu comentários denecessários</t>
+  </si>
+  <si>
+    <t>Configurou as dietrize de personalidade com ética observando a LGPD</t>
+  </si>
+  <si>
+    <t>Fez deploy no GitHub Pages com eficácia</t>
+  </si>
+  <si>
+    <t>Conectou uma API de IA Gemini ou outra ao projeto com eficácia em produção</t>
+  </si>
+  <si>
+    <t>Compreendeu as instruções técnicas do desafio</t>
+  </si>
+  <si>
+    <t>Uitlizou a IA como apoio a produtividade compreendendo os códigos gerados</t>
+  </si>
+  <si>
+    <t>Executou todas as tarefas inerentes a atividade</t>
+  </si>
+  <si>
+    <t>Obedeceu as regras de qualidade no desenvolvimento de UI (User Interface)</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 5 dos 14 desejáveis</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 7 dos 14 desejáveis</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 9 dos 14 desejáveis</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 11 dos 14 desejáveis</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 12 dos 14 desejáveis</t>
+  </si>
+  <si>
+    <t>Acertou todos os critérios críticos e pelo menos 13 dos 14 desejáveis</t>
+  </si>
 </sst>
 </file>
 
@@ -527,7 +599,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm"/>
     <numFmt numFmtId="165" formatCode="d/m"/>
   </numFmts>
-  <fonts count="48" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,12 +766,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -804,23 +870,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Segoe UI"/>
@@ -836,6 +885,24 @@
       <sz val="16.5"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1290,9 +1357,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1333,31 +1400,31 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1378,79 +1445,145 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1458,6 +1591,53 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1467,7 +1647,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1491,218 +1674,94 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1966,7 +2025,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AA960"/>
+  <dimension ref="A2:AA964"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.09765625" customWidth="1"/>
@@ -1983,134 +2042,134 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
     </row>
     <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="48" t="s">
+      <c r="B3" s="129"/>
+      <c r="C3" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="42" t="s">
+      <c r="D3" s="121"/>
+      <c r="E3" s="124" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="125"/>
+      <c r="G3" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42" t="s">
+      <c r="H3" s="115"/>
+      <c r="I3" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="42"/>
+      <c r="J3" s="115"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="50" t="s">
+      <c r="A4" s="128"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="122"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="127"/>
+      <c r="G4" s="114" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="114"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+    </row>
+    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="102"/>
+      <c r="C5" s="104" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="105"/>
+      <c r="E5" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="109"/>
+      <c r="G5" s="114" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+    </row>
+    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="102"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="110" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="111"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="105"/>
+    </row>
+    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="102"/>
+      <c r="C7" s="106" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="106"/>
+      <c r="E7" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="51"/>
-      <c r="G4" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-    </row>
-    <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="61"/>
-      <c r="C5" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="67"/>
-      <c r="G5" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-    </row>
-    <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
-      <c r="B6" s="62"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="69"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-    </row>
-    <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="71"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
     </row>
     <row r="8" spans="1:27" ht="109.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="61"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
     </row>
     <row r="9" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
     </row>
     <row r="10" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
@@ -2131,14 +2190,14 @@
       <c r="F10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55" t="s">
+      <c r="H10" s="116"/>
+      <c r="I10" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="55"/>
+      <c r="J10" s="116"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2159,31 +2218,31 @@
     </row>
     <row r="11" spans="1:27" ht="255" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="21">
         <v>8</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="100" t="s">
+      <c r="G11" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="58" t="s">
-        <v>52</v>
+      <c r="H11" s="83"/>
+      <c r="I11" s="117" t="s">
+        <v>89</v>
       </c>
-      <c r="H11" s="59"/>
-      <c r="I11" s="56" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" s="57"/>
+      <c r="J11" s="118"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2204,29 +2263,29 @@
     </row>
     <row r="12" spans="1:27" ht="132" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
-      <c r="E12" s="103" t="s">
-        <v>62</v>
+      <c r="E12" s="80" t="s">
+        <v>60</v>
       </c>
-      <c r="F12" s="101"/>
-      <c r="G12" s="58" t="s">
-        <v>89</v>
+      <c r="F12" s="78"/>
+      <c r="G12" s="82" t="s">
+        <v>87</v>
       </c>
-      <c r="H12" s="59"/>
-      <c r="I12" s="110" t="s">
-        <v>90</v>
+      <c r="H12" s="83"/>
+      <c r="I12" s="89" t="s">
+        <v>88</v>
       </c>
-      <c r="J12" s="111"/>
+      <c r="J12" s="90"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2247,27 +2306,27 @@
     </row>
     <row r="13" spans="1:27" ht="267.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="13">
         <v>16</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
-      <c r="E13" s="104"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="58" t="s">
-        <v>94</v>
+      <c r="E13" s="81"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="82" t="s">
+        <v>92</v>
       </c>
-      <c r="H13" s="59"/>
-      <c r="I13" s="147" t="s">
-        <v>93</v>
+      <c r="H13" s="83"/>
+      <c r="I13" s="70" t="s">
+        <v>91</v>
       </c>
-      <c r="J13" s="148"/>
+      <c r="J13" s="71"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2288,27 +2347,27 @@
     </row>
     <row r="14" spans="1:27" ht="198" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="13">
         <v>12</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D14" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="32" t="s">
-        <v>63</v>
+      <c r="F14" s="79"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="72" t="s">
+        <v>90</v>
       </c>
-      <c r="F14" s="102"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="95" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="96"/>
+      <c r="J14" s="73"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2339,10 +2398,10 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="109"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="87"/>
+      <c r="J15" s="88"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2362,18 +2421,18 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="97" t="s">
-        <v>40</v>
+      <c r="A16" s="74" t="s">
+        <v>38</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="99"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="76"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2393,18 +2452,18 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="129" t="s">
-        <v>64</v>
+      <c r="A17" s="52" t="s">
+        <v>62</v>
       </c>
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2424,18 +2483,18 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="76.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="131" t="s">
-        <v>65</v>
+      <c r="A18" s="50" t="s">
+        <v>63</v>
       </c>
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="132"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2455,18 +2514,18 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="130" t="s">
+      <c r="A19" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="130"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="130"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2486,18 +2545,18 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="116.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="131" t="s">
-        <v>66</v>
+      <c r="A20" s="50" t="s">
+        <v>64</v>
       </c>
-      <c r="B20" s="132"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="132"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2517,18 +2576,18 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A21" s="130" t="s">
+      <c r="A21" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="130"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="130"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="130"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2548,18 +2607,18 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="228.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="131" t="s">
-        <v>67</v>
+      <c r="A22" s="50" t="s">
+        <v>65</v>
       </c>
-      <c r="B22" s="131"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2579,16 +2638,16 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="136"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="137"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="137"/>
-      <c r="H23" s="137"/>
-      <c r="I23" s="137"/>
-      <c r="J23" s="138"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="59"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2608,18 +2667,18 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="139" t="s">
+      <c r="A24" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="139"/>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="139"/>
-      <c r="J24" s="139"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2639,22 +2698,22 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="133" t="s">
+      <c r="A25" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="134"/>
-      <c r="C25" s="134"/>
-      <c r="D25" s="135" t="s">
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="135"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="140" t="s">
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="115"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="115"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
+      <c r="J25" s="49"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2674,12 +2733,12 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A26" s="134"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
+      <c r="A26" s="55"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
       <c r="G26" s="19">
         <v>1</v>
       </c>
@@ -2711,16 +2770,18 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="120" t="s">
-        <v>51</v>
+      <c r="B27" s="130" t="s">
+        <v>49</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="88"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="132" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="133"/>
+      <c r="F27" s="134"/>
       <c r="G27" s="37"/>
       <c r="H27" s="38"/>
       <c r="I27" s="39"/>
@@ -2744,12 +2805,14 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
-      <c r="B28" s="122"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="88"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="135"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="137" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="138"/>
+      <c r="F28" s="134"/>
       <c r="G28" s="37"/>
       <c r="H28" s="38"/>
       <c r="I28" s="40"/>
@@ -2773,14 +2836,16 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
-      <c r="B29" s="127" t="s">
-        <v>81</v>
+      <c r="A29" s="99"/>
+      <c r="B29" s="139" t="s">
+        <v>79</v>
       </c>
-      <c r="C29" s="128"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="79"/>
-      <c r="F29" s="80"/>
+      <c r="C29" s="140"/>
+      <c r="D29" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="133"/>
+      <c r="F29" s="134"/>
       <c r="G29" s="37"/>
       <c r="H29" s="38"/>
       <c r="I29" s="40"/>
@@ -2804,12 +2869,14 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="85"/>
-      <c r="B30" s="122"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="80"/>
+      <c r="A30" s="99"/>
+      <c r="B30" s="135"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="137" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="138"/>
+      <c r="F30" s="134"/>
       <c r="G30" s="37"/>
       <c r="H30" s="38"/>
       <c r="I30" s="40"/>
@@ -2833,14 +2900,16 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="85"/>
-      <c r="B31" s="127" t="s">
-        <v>82</v>
+      <c r="A31" s="99"/>
+      <c r="B31" s="139" t="s">
+        <v>80</v>
       </c>
-      <c r="C31" s="128"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="79"/>
-      <c r="F31" s="80"/>
+      <c r="C31" s="140"/>
+      <c r="D31" s="132" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="133"/>
+      <c r="F31" s="134"/>
       <c r="G31" s="37"/>
       <c r="H31" s="38"/>
       <c r="I31" s="40"/>
@@ -2864,12 +2933,14 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="85"/>
-      <c r="B32" s="122"/>
-      <c r="C32" s="123"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="80"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="135"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="137" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="138"/>
+      <c r="F32" s="134"/>
       <c r="G32" s="37"/>
       <c r="H32" s="38"/>
       <c r="I32" s="40"/>
@@ -2893,14 +2964,16 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="85"/>
-      <c r="B33" s="127" t="s">
-        <v>83</v>
+      <c r="A33" s="99"/>
+      <c r="B33" s="139" t="s">
+        <v>81</v>
       </c>
-      <c r="C33" s="128"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="79"/>
-      <c r="F33" s="80"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="132" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="133"/>
+      <c r="F33" s="134"/>
       <c r="G33" s="37"/>
       <c r="H33" s="38"/>
       <c r="I33" s="40"/>
@@ -2924,12 +2997,14 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="85"/>
-      <c r="B34" s="122"/>
-      <c r="C34" s="123"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="79"/>
-      <c r="F34" s="80"/>
+      <c r="A34" s="99"/>
+      <c r="B34" s="135"/>
+      <c r="C34" s="136"/>
+      <c r="D34" s="137" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="138"/>
+      <c r="F34" s="134"/>
       <c r="G34" s="37"/>
       <c r="H34" s="38"/>
       <c r="I34" s="40"/>
@@ -2953,14 +3028,16 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="85"/>
-      <c r="B35" s="127" t="s">
-        <v>84</v>
+      <c r="A35" s="99"/>
+      <c r="B35" s="139" t="s">
+        <v>82</v>
       </c>
-      <c r="C35" s="128"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="80"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="133"/>
+      <c r="F35" s="134"/>
       <c r="G35" s="37"/>
       <c r="H35" s="38"/>
       <c r="I35" s="40"/>
@@ -2984,12 +3061,14 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="85"/>
-      <c r="B36" s="122"/>
-      <c r="C36" s="123"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="135"/>
+      <c r="C36" s="136"/>
+      <c r="D36" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="138"/>
+      <c r="F36" s="134"/>
       <c r="G36" s="37"/>
       <c r="H36" s="38"/>
       <c r="I36" s="40"/>
@@ -3013,14 +3092,16 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="85"/>
-      <c r="B37" s="127" t="s">
-        <v>85</v>
+      <c r="A37" s="99"/>
+      <c r="B37" s="139" t="s">
+        <v>83</v>
       </c>
-      <c r="C37" s="128"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="80"/>
+      <c r="C37" s="140"/>
+      <c r="D37" s="132" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" s="133"/>
+      <c r="F37" s="134"/>
       <c r="G37" s="37"/>
       <c r="H37" s="38"/>
       <c r="I37" s="40"/>
@@ -3044,12 +3125,14 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="85"/>
-      <c r="B38" s="122"/>
-      <c r="C38" s="123"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="80"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="135"/>
+      <c r="C38" s="136"/>
+      <c r="D38" s="137" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="138"/>
+      <c r="F38" s="134"/>
       <c r="G38" s="37"/>
       <c r="H38" s="38"/>
       <c r="I38" s="40"/>
@@ -3073,14 +3156,16 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="85"/>
-      <c r="B39" s="127" t="s">
-        <v>55</v>
+      <c r="A39" s="99"/>
+      <c r="B39" s="139" t="s">
+        <v>53</v>
       </c>
-      <c r="C39" s="128"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="80"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="141" t="s">
+        <v>126</v>
+      </c>
+      <c r="E39" s="142"/>
+      <c r="F39" s="143"/>
       <c r="G39" s="37"/>
       <c r="H39" s="38"/>
       <c r="I39" s="40"/>
@@ -3104,12 +3189,14 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="32.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="85"/>
-      <c r="B40" s="122"/>
-      <c r="C40" s="123"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="80"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="135"/>
+      <c r="C40" s="136"/>
+      <c r="D40" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="142"/>
+      <c r="F40" s="143"/>
       <c r="G40" s="37"/>
       <c r="H40" s="38"/>
       <c r="I40" s="40"/>
@@ -3133,14 +3220,16 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="85"/>
-      <c r="B41" s="127" t="s">
-        <v>86</v>
+      <c r="A41" s="99"/>
+      <c r="B41" s="139" t="s">
+        <v>84</v>
       </c>
-      <c r="C41" s="128"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="79"/>
-      <c r="F41" s="80"/>
+      <c r="C41" s="140"/>
+      <c r="D41" s="141" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="142"/>
+      <c r="F41" s="143"/>
       <c r="G41" s="37"/>
       <c r="H41" s="38"/>
       <c r="I41" s="40"/>
@@ -3164,12 +3253,14 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="85"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="79"/>
-      <c r="F42" s="80"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="135"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="141" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" s="142"/>
+      <c r="F42" s="143"/>
       <c r="G42" s="37"/>
       <c r="H42" s="38"/>
       <c r="I42" s="40"/>
@@ -3193,14 +3284,16 @@
       <c r="AA42" s="1"/>
     </row>
     <row r="43" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="119"/>
-      <c r="B43" s="120" t="s">
-        <v>87</v>
+      <c r="A43" s="100"/>
+      <c r="B43" s="130" t="s">
+        <v>85</v>
       </c>
-      <c r="C43" s="121"/>
-      <c r="D43" s="124"/>
-      <c r="E43" s="125"/>
-      <c r="F43" s="126"/>
+      <c r="C43" s="131"/>
+      <c r="D43" s="144" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="145"/>
+      <c r="F43" s="146"/>
       <c r="G43" s="37"/>
       <c r="H43" s="38"/>
       <c r="I43" s="40"/>
@@ -3224,12 +3317,14 @@
       <c r="AA43" s="1"/>
     </row>
     <row r="44" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="119"/>
-      <c r="B44" s="122"/>
-      <c r="C44" s="123"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="82"/>
-      <c r="F44" s="83"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="144" t="s">
+        <v>132</v>
+      </c>
+      <c r="E44" s="145"/>
+      <c r="F44" s="146"/>
       <c r="G44" s="37"/>
       <c r="H44" s="38"/>
       <c r="I44" s="40"/>
@@ -3253,14 +3348,16 @@
       <c r="AA44" s="1"/>
     </row>
     <row r="45" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="119"/>
-      <c r="B45" s="127" t="s">
-        <v>88</v>
+      <c r="A45" s="100"/>
+      <c r="B45" s="139" t="s">
+        <v>86</v>
       </c>
-      <c r="C45" s="128"/>
-      <c r="D45" s="124"/>
-      <c r="E45" s="125"/>
-      <c r="F45" s="126"/>
+      <c r="C45" s="140"/>
+      <c r="D45" s="144" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="145"/>
+      <c r="F45" s="146"/>
       <c r="G45" s="37"/>
       <c r="H45" s="38"/>
       <c r="I45" s="40"/>
@@ -3284,12 +3381,14 @@
       <c r="AA45" s="1"/>
     </row>
     <row r="46" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="119"/>
-      <c r="B46" s="122"/>
-      <c r="C46" s="123"/>
-      <c r="D46" s="81"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="83"/>
+      <c r="A46" s="100"/>
+      <c r="B46" s="135"/>
+      <c r="C46" s="136"/>
+      <c r="D46" s="144" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="145"/>
+      <c r="F46" s="146"/>
       <c r="G46" s="37"/>
       <c r="H46" s="38"/>
       <c r="I46" s="40"/>
@@ -3313,14 +3412,14 @@
       <c r="AA46" s="1"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="76"/>
-      <c r="B47" s="77"/>
-      <c r="C47" s="77"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
+      <c r="A47" s="96"/>
+      <c r="B47" s="97"/>
+      <c r="C47" s="97"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3342,18 +3441,18 @@
       <c r="AA47" s="1"/>
     </row>
     <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="72" t="s">
+      <c r="A48" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="75" t="s">
+      <c r="B48" s="93"/>
+      <c r="C48" s="93"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="94"/>
+      <c r="F48" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="G48" s="73"/>
-      <c r="H48" s="74"/>
+      <c r="G48" s="93"/>
+      <c r="H48" s="94"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -3374,21 +3473,21 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
     </row>
-    <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
-      <c r="B49" s="93" t="s">
+      <c r="B49" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="91"/>
-      <c r="F49" s="92">
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="64">
         <v>100</v>
       </c>
-      <c r="G49" s="90"/>
-      <c r="H49" s="91"/>
+      <c r="G49" s="62"/>
+      <c r="H49" s="63"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -3409,21 +3508,21 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
     </row>
-    <row r="50" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
-      <c r="B50" s="94" t="s">
-        <v>39</v>
+      <c r="B50" s="61" t="s">
+        <v>140</v>
       </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="91"/>
-      <c r="F50" s="92">
-        <v>80</v>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="64">
+        <v>95</v>
       </c>
-      <c r="G50" s="90"/>
-      <c r="H50" s="91"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="63"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -3444,21 +3543,21 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
     </row>
-    <row r="51" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
-      <c r="B51" s="94" t="s">
-        <v>38</v>
+      <c r="B51" s="61" t="s">
+        <v>139</v>
       </c>
-      <c r="C51" s="90"/>
-      <c r="D51" s="90"/>
-      <c r="E51" s="91"/>
-      <c r="F51" s="92">
-        <v>65</v>
+      <c r="C51" s="62"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="64">
+        <v>90</v>
       </c>
-      <c r="G51" s="90"/>
-      <c r="H51" s="91"/>
+      <c r="G51" s="62"/>
+      <c r="H51" s="63"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -3479,21 +3578,21 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
     </row>
-    <row r="52" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
-      <c r="B52" s="89" t="s">
-        <v>15</v>
+      <c r="B52" s="61" t="s">
+        <v>138</v>
       </c>
-      <c r="C52" s="90"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="91"/>
-      <c r="F52" s="92">
-        <v>50</v>
+      <c r="C52" s="62"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="64">
+        <v>85</v>
       </c>
-      <c r="G52" s="90"/>
-      <c r="H52" s="91"/>
+      <c r="G52" s="62"/>
+      <c r="H52" s="63"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -3514,21 +3613,21 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
     </row>
-    <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
-      <c r="B53" s="93" t="s">
-        <v>16</v>
+      <c r="B53" s="61" t="s">
+        <v>137</v>
       </c>
-      <c r="C53" s="90"/>
-      <c r="D53" s="90"/>
-      <c r="E53" s="91"/>
-      <c r="F53" s="92">
-        <v>30</v>
+      <c r="C53" s="62"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="64">
+        <v>80</v>
       </c>
-      <c r="G53" s="90"/>
-      <c r="H53" s="91"/>
+      <c r="G53" s="62"/>
+      <c r="H53" s="63"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -3549,15 +3648,21 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
     </row>
-    <row r="54" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
+    <row r="54" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="7">
+        <v>4</v>
+      </c>
+      <c r="B54" s="61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="64">
+        <v>70</v>
+      </c>
+      <c r="G54" s="62"/>
+      <c r="H54" s="63"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -3578,21 +3683,21 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
     </row>
-    <row r="55" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="16" t="s">
-        <v>17</v>
+    <row r="55" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="7">
+        <v>3</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>18</v>
+      <c r="B55" s="61" t="s">
+        <v>135</v>
       </c>
-      <c r="F55" s="16" t="s">
-        <v>19</v>
+      <c r="C55" s="62"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="64">
+        <v>60</v>
       </c>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
+      <c r="G55" s="62"/>
+      <c r="H55" s="63"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -3613,25 +3718,21 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
     </row>
-    <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="17" t="s">
-        <v>20</v>
+    <row r="56" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="7">
+        <v>2</v>
       </c>
-      <c r="E56" s="113">
-        <v>1</v>
+      <c r="B56" s="91" t="s">
+        <v>15</v>
       </c>
-      <c r="F56" s="113">
-        <v>0</v>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="64">
+        <v>50</v>
       </c>
-      <c r="G56" s="115" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="117" t="s">
-        <v>22</v>
-      </c>
+      <c r="G56" s="62"/>
+      <c r="H56" s="63"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -3653,16 +3754,20 @@
       <c r="AA56" s="1"/>
     </row>
     <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="24" t="s">
-        <v>23</v>
+      <c r="A57" s="7">
+        <v>1</v>
       </c>
-      <c r="E57" s="114"/>
-      <c r="F57" s="114"/>
-      <c r="G57" s="116"/>
-      <c r="H57" s="118"/>
+      <c r="B57" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="62"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="64">
+        <v>30</v>
+      </c>
+      <c r="G57" s="62"/>
+      <c r="H57" s="63"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -3684,18 +3789,16 @@
       <c r="AA57" s="1"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="112" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="112"/>
-      <c r="C58" s="112"/>
-      <c r="D58" s="112"/>
-      <c r="E58" s="112"/>
-      <c r="F58" s="112"/>
-      <c r="G58" s="112"/>
-      <c r="H58" s="112"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="112"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3714,17 +3817,23 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
     </row>
-    <row r="59" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="112"/>
-      <c r="B59" s="112"/>
-      <c r="C59" s="112"/>
-      <c r="D59" s="112"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="112"/>
-      <c r="G59" s="112"/>
-      <c r="H59" s="112"/>
-      <c r="I59" s="112"/>
-      <c r="J59" s="112"/>
+    <row r="59" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3743,15 +3852,25 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
     </row>
-    <row r="60" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="4"/>
+    <row r="60" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="65">
+        <v>1</v>
+      </c>
+      <c r="F60" s="65">
+        <v>0</v>
+      </c>
+      <c r="G60" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="68" t="s">
+        <v>22</v>
+      </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -3772,15 +3891,17 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
     </row>
-    <row r="61" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="4"/>
+    <row r="61" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="69"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -3802,16 +3923,18 @@
       <c r="AA61" s="1"/>
     </row>
     <row r="62" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
+      <c r="A62" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B62" s="60"/>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="60"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -3831,16 +3954,16 @@
       <c r="AA62" s="1"/>
     </row>
     <row r="63" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
+      <c r="A63" s="60"/>
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="60"/>
+      <c r="J63" s="60"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
@@ -7426,121 +7549,121 @@
       <c r="Z186" s="1"/>
       <c r="AA186" s="1"/>
     </row>
-    <row r="187" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
-      <c r="L187" s="6"/>
-      <c r="M187" s="6"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="6"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="6"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="6"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="6"/>
-    </row>
-    <row r="188" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
-      <c r="M188" s="6"/>
-      <c r="N188" s="6"/>
-      <c r="O188" s="6"/>
-      <c r="P188" s="6"/>
-      <c r="Q188" s="6"/>
-      <c r="R188" s="6"/>
-      <c r="S188" s="6"/>
-      <c r="T188" s="6"/>
-      <c r="U188" s="6"/>
-      <c r="V188" s="6"/>
-      <c r="W188" s="6"/>
-      <c r="X188" s="6"/>
-      <c r="Y188" s="6"/>
-      <c r="Z188" s="6"/>
-      <c r="AA188" s="6"/>
-    </row>
-    <row r="189" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6"/>
-      <c r="M189" s="6"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="6"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="6"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="6"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="6"/>
-    </row>
-    <row r="190" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-      <c r="J190" s="6"/>
-      <c r="K190" s="6"/>
-      <c r="L190" s="6"/>
-      <c r="M190" s="6"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="6"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="6"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="6"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="6"/>
+    <row r="187" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="1"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+      <c r="E187" s="1"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="5"/>
+      <c r="H187" s="4"/>
+      <c r="I187" s="1"/>
+      <c r="J187" s="1"/>
+      <c r="K187" s="1"/>
+      <c r="L187" s="1"/>
+      <c r="M187" s="1"/>
+      <c r="N187" s="1"/>
+      <c r="O187" s="1"/>
+      <c r="P187" s="1"/>
+      <c r="Q187" s="1"/>
+      <c r="R187" s="1"/>
+      <c r="S187" s="1"/>
+      <c r="T187" s="1"/>
+      <c r="U187" s="1"/>
+      <c r="V187" s="1"/>
+      <c r="W187" s="1"/>
+      <c r="X187" s="1"/>
+      <c r="Y187" s="1"/>
+      <c r="Z187" s="1"/>
+      <c r="AA187" s="1"/>
+    </row>
+    <row r="188" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="1"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+      <c r="E188" s="1"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="4"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+      <c r="L188" s="1"/>
+      <c r="M188" s="1"/>
+      <c r="N188" s="1"/>
+      <c r="O188" s="1"/>
+      <c r="P188" s="1"/>
+      <c r="Q188" s="1"/>
+      <c r="R188" s="1"/>
+      <c r="S188" s="1"/>
+      <c r="T188" s="1"/>
+      <c r="U188" s="1"/>
+      <c r="V188" s="1"/>
+      <c r="W188" s="1"/>
+      <c r="X188" s="1"/>
+      <c r="Y188" s="1"/>
+      <c r="Z188" s="1"/>
+      <c r="AA188" s="1"/>
+    </row>
+    <row r="189" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="1"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+      <c r="E189" s="1"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="4"/>
+      <c r="I189" s="1"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
+      <c r="L189" s="1"/>
+      <c r="M189" s="1"/>
+      <c r="N189" s="1"/>
+      <c r="O189" s="1"/>
+      <c r="P189" s="1"/>
+      <c r="Q189" s="1"/>
+      <c r="R189" s="1"/>
+      <c r="S189" s="1"/>
+      <c r="T189" s="1"/>
+      <c r="U189" s="1"/>
+      <c r="V189" s="1"/>
+      <c r="W189" s="1"/>
+      <c r="X189" s="1"/>
+      <c r="Y189" s="1"/>
+      <c r="Z189" s="1"/>
+      <c r="AA189" s="1"/>
+    </row>
+    <row r="190" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="1"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+      <c r="E190" s="1"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="5"/>
+      <c r="H190" s="4"/>
+      <c r="I190" s="1"/>
+      <c r="J190" s="1"/>
+      <c r="K190" s="1"/>
+      <c r="L190" s="1"/>
+      <c r="M190" s="1"/>
+      <c r="N190" s="1"/>
+      <c r="O190" s="1"/>
+      <c r="P190" s="1"/>
+      <c r="Q190" s="1"/>
+      <c r="R190" s="1"/>
+      <c r="S190" s="1"/>
+      <c r="T190" s="1"/>
+      <c r="U190" s="1"/>
+      <c r="V190" s="1"/>
+      <c r="W190" s="1"/>
+      <c r="X190" s="1"/>
+      <c r="Y190" s="1"/>
+      <c r="Z190" s="1"/>
+      <c r="AA190" s="1"/>
     </row>
     <row r="191" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6"/>
@@ -29872,22 +29995,197 @@
       <c r="Z960" s="6"/>
       <c r="AA960" s="6"/>
     </row>
+    <row r="961" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A961" s="6"/>
+      <c r="B961" s="6"/>
+      <c r="C961" s="6"/>
+      <c r="D961" s="6"/>
+      <c r="E961" s="6"/>
+      <c r="F961" s="6"/>
+      <c r="G961" s="6"/>
+      <c r="H961" s="6"/>
+      <c r="I961" s="6"/>
+      <c r="J961" s="6"/>
+      <c r="K961" s="6"/>
+      <c r="L961" s="6"/>
+      <c r="M961" s="6"/>
+      <c r="N961" s="6"/>
+      <c r="O961" s="6"/>
+      <c r="P961" s="6"/>
+      <c r="Q961" s="6"/>
+      <c r="R961" s="6"/>
+      <c r="S961" s="6"/>
+      <c r="T961" s="6"/>
+      <c r="U961" s="6"/>
+      <c r="V961" s="6"/>
+      <c r="W961" s="6"/>
+      <c r="X961" s="6"/>
+      <c r="Y961" s="6"/>
+      <c r="Z961" s="6"/>
+      <c r="AA961" s="6"/>
+    </row>
+    <row r="962" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A962" s="6"/>
+      <c r="B962" s="6"/>
+      <c r="C962" s="6"/>
+      <c r="D962" s="6"/>
+      <c r="E962" s="6"/>
+      <c r="F962" s="6"/>
+      <c r="G962" s="6"/>
+      <c r="H962" s="6"/>
+      <c r="I962" s="6"/>
+      <c r="J962" s="6"/>
+      <c r="K962" s="6"/>
+      <c r="L962" s="6"/>
+      <c r="M962" s="6"/>
+      <c r="N962" s="6"/>
+      <c r="O962" s="6"/>
+      <c r="P962" s="6"/>
+      <c r="Q962" s="6"/>
+      <c r="R962" s="6"/>
+      <c r="S962" s="6"/>
+      <c r="T962" s="6"/>
+      <c r="U962" s="6"/>
+      <c r="V962" s="6"/>
+      <c r="W962" s="6"/>
+      <c r="X962" s="6"/>
+      <c r="Y962" s="6"/>
+      <c r="Z962" s="6"/>
+      <c r="AA962" s="6"/>
+    </row>
+    <row r="963" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A963" s="6"/>
+      <c r="B963" s="6"/>
+      <c r="C963" s="6"/>
+      <c r="D963" s="6"/>
+      <c r="E963" s="6"/>
+      <c r="F963" s="6"/>
+      <c r="G963" s="6"/>
+      <c r="H963" s="6"/>
+      <c r="I963" s="6"/>
+      <c r="J963" s="6"/>
+      <c r="K963" s="6"/>
+      <c r="L963" s="6"/>
+      <c r="M963" s="6"/>
+      <c r="N963" s="6"/>
+      <c r="O963" s="6"/>
+      <c r="P963" s="6"/>
+      <c r="Q963" s="6"/>
+      <c r="R963" s="6"/>
+      <c r="S963" s="6"/>
+      <c r="T963" s="6"/>
+      <c r="U963" s="6"/>
+      <c r="V963" s="6"/>
+      <c r="W963" s="6"/>
+      <c r="X963" s="6"/>
+      <c r="Y963" s="6"/>
+      <c r="Z963" s="6"/>
+      <c r="AA963" s="6"/>
+    </row>
+    <row r="964" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A964" s="6"/>
+      <c r="B964" s="6"/>
+      <c r="C964" s="6"/>
+      <c r="D964" s="6"/>
+      <c r="E964" s="6"/>
+      <c r="F964" s="6"/>
+      <c r="G964" s="6"/>
+      <c r="H964" s="6"/>
+      <c r="I964" s="6"/>
+      <c r="J964" s="6"/>
+      <c r="K964" s="6"/>
+      <c r="L964" s="6"/>
+      <c r="M964" s="6"/>
+      <c r="N964" s="6"/>
+      <c r="O964" s="6"/>
+      <c r="P964" s="6"/>
+      <c r="Q964" s="6"/>
+      <c r="R964" s="6"/>
+      <c r="S964" s="6"/>
+      <c r="T964" s="6"/>
+      <c r="U964" s="6"/>
+      <c r="V964" s="6"/>
+      <c r="W964" s="6"/>
+      <c r="X964" s="6"/>
+      <c r="Y964" s="6"/>
+      <c r="Z964" s="6"/>
+      <c r="AA964" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="95">
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="D31:F31"/>
+  <mergeCells count="103">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J8"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="A27:A42"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B43:C44"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="B45:C46"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A62:J63"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
     <mergeCell ref="B41:C42"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="D42:F42"/>
@@ -29904,73 +30202,22 @@
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="D29:F29"/>
-    <mergeCell ref="A58:J59"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="G56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="A27:A42"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B43:C44"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B45:C46"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G6:J8"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="C3:D4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D40:F40"/>
   </mergeCells>
-  <phoneticPr fontId="32" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I12:J12" location="Desafio01!A1" display="Solucionar um desafio com ajuda de uma IA generativa  e deixar púbico no GitHub Pages." xr:uid="{C34EA30B-E5B1-4472-B11D-DD22B093A071}"/>
     <hyperlink ref="I13:J13" location="PortFolio!A1" display="Exposição dialogada, demonstrações, criação de um portifolio web público com pelo menos dois projetos concluídos ou em andamento." xr:uid="{07706612-ED63-4036-B091-EDE307D89F89}"/>
@@ -29995,67 +30242,67 @@
   <sheetData>
     <row r="1" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+    <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+    <row r="6" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+    <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
+    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="36" t="s">
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+    <row r="12" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A12" s="35" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
-        <v>79</v>
-      </c>
-    </row>
     <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -30072,118 +30319,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="41" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="43" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="142" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="145" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="145" t="s">
+    <row r="8" spans="1:1" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="145" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="145" t="s">
+    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="145" t="s">
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="144" t="s">
+    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="144" t="s">
+    <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="142" t="s">
+    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="144" t="s">
+    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="42" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="144" t="s">
+    <row r="20" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="142" t="s">
+    <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="41" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="146" t="s">
+    <row r="23" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="141" t="s">
+    <row r="25" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
-      <c r="A23" s="146" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="144" t="s">
+    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="44" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="144" t="s">
+    <row r="28" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="144" t="s">
+    <row r="30" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="44" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="25.2" x14ac:dyDescent="0.25">
-      <c r="A28" s="146" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="144" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="144" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
